--- a/reports/빅딜/빅딜_mgf_matched_5_guilds.xlsx
+++ b/reports/빅딜/빅딜_mgf_matched_5_guilds.xlsx
@@ -20,14 +20,14 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">부계둘!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">이고이스트!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">피난민!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">피난민!$A$1:$J$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1588" uniqueCount="561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1578" uniqueCount="558">
   <si>
     <t>guild_name</t>
   </si>
@@ -743,22 +743,22 @@
     <t>2조 1548억 7397만</t>
   </si>
   <si>
+    <t>상산의조자룡</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EC%82%B0%EC%9D%98%EC%A1%B0%EC%9E%90%EB%A3%A1</t>
+  </si>
+  <si>
+    <t>2조 336억 4951만</t>
+  </si>
+  <si>
     <t>샾프심</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%ED%94%84%EC%8B%AC</t>
   </si>
   <si>
-    <t>1조 9835억 2177만</t>
-  </si>
-  <si>
-    <t>상산의조자룡</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EC%82%B0%EC%9D%98%EC%A1%B0%EC%9E%90%EB%A3%A1</t>
-  </si>
-  <si>
-    <t>1조 9330억 1850만</t>
+    <t>1조 9865억 8595만</t>
   </si>
   <si>
     <t>김퍽퍽</t>
@@ -848,24 +848,15 @@
     <t>3926억 8648만</t>
   </si>
   <si>
-    <t>샾영세</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%98%81%EC%84%B8</t>
+    <t>긩섷</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%A9%EC%84%B7</t>
   </si>
   <si>
     <t>93</t>
   </si>
   <si>
-    <t>3444억 1454만</t>
-  </si>
-  <si>
-    <t>긩섷</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%A9%EC%84%B7</t>
-  </si>
-  <si>
     <t>1822억 4872만</t>
   </si>
   <si>
@@ -917,274 +908,274 @@
     <t>1283억 4276만</t>
   </si>
   <si>
+    <t>커피둥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%ED%94%BC%EB%91%A5</t>
+  </si>
+  <si>
+    <t>1119억 5831만</t>
+  </si>
+  <si>
+    <t>마퀸</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%ED%80%B8</t>
+  </si>
+  <si>
+    <t>39조 7974억 3406만</t>
+  </si>
+  <si>
+    <t>라면에계란탁</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EB%A9%B4%EC%97%90%EA%B3%84%EB%9E%80%ED%83%81</t>
+  </si>
+  <si>
+    <t>25조 8518억 9060만</t>
+  </si>
+  <si>
+    <t>에이비숍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EC%9D%B4%EB%B9%84%EC%88%8D</t>
+  </si>
+  <si>
+    <t>17조 4527억 529만</t>
+  </si>
+  <si>
+    <t>이금기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EA%B8%88%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>11조 3968억 6209만</t>
+  </si>
+  <si>
+    <t>환불카드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EB%B6%88%EC%B9%B4%EB%93%9C</t>
+  </si>
+  <si>
+    <t>7조 8198억 8819만</t>
+  </si>
+  <si>
+    <t>아빠카드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%B9%A0%EC%B9%B4%EB%93%9C</t>
+  </si>
+  <si>
+    <t>6조 1256억 7831만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%8F%84%EC%B9%B4%EB%93%9C</t>
+  </si>
+  <si>
+    <t>4조 1085억 3018만</t>
+  </si>
+  <si>
+    <t>시글</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EA%B8%80</t>
+  </si>
+  <si>
+    <t>4조 156억 2084만</t>
+  </si>
+  <si>
+    <t>공사과장</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EC%82%AC%EA%B3%BC%EC%9E%A5</t>
+  </si>
+  <si>
+    <t>1조 8947억 4945만</t>
+  </si>
+  <si>
+    <t>사과닷</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EA%B3%BC%EB%8B%B7</t>
+  </si>
+  <si>
+    <t>1조 7309억 6750만</t>
+  </si>
+  <si>
+    <t>토이감자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EC%9D%B4%EA%B0%90%EC%9E%90</t>
+  </si>
+  <si>
+    <t>1조 2864억 1536만</t>
+  </si>
+  <si>
+    <t>Eddy0825</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Eddy0825</t>
+  </si>
+  <si>
+    <t>1조 2641억 5580만</t>
+  </si>
+  <si>
+    <t>히히맘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%ED%9E%88%EB%A7%98</t>
+  </si>
+  <si>
+    <t>1조 1551억 3755만</t>
+  </si>
+  <si>
+    <t>망치전문</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%98%EC%A0%84%EB%AC%B8</t>
+  </si>
+  <si>
+    <t>1조 927억 6855만</t>
+  </si>
+  <si>
+    <t>핑와스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%91%EC%99%80%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>8953억 4884만</t>
+  </si>
+  <si>
+    <t>호츠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%B8%A0</t>
+  </si>
+  <si>
+    <t>8232억 647만</t>
+  </si>
+  <si>
+    <t>돌격대원</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EA%B2%A9%EB%8C%80%EC%9B%90</t>
+  </si>
+  <si>
+    <t>8183억 3301만</t>
+  </si>
+  <si>
+    <t>닉커</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%89%EC%BB%A4</t>
+  </si>
+  <si>
+    <t>8061억 7543만</t>
+  </si>
+  <si>
+    <t>비숍덩구</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%88%8D%EB%8D%A9%EA%B5%AC</t>
+  </si>
+  <si>
+    <t>7662억 1359만</t>
+  </si>
+  <si>
+    <t>단풍a</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8Da</t>
+  </si>
+  <si>
+    <t>7563억 4292만</t>
+  </si>
+  <si>
+    <t>문뚱식</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%9A%B1%EC%8B%9D</t>
+  </si>
+  <si>
+    <t>7185억 5363만</t>
+  </si>
+  <si>
+    <t>회원카드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9A%8C%EC%9B%90%EC%B9%B4%EB%93%9C</t>
+  </si>
+  <si>
+    <t>7126억 7783만</t>
+  </si>
+  <si>
+    <t>떼링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%96%BC%EB%A7%81</t>
+  </si>
+  <si>
+    <t>6842억 7643만</t>
+  </si>
+  <si>
+    <t>오보기다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%B3%B4%EA%B8%B0%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>6741억 7723만</t>
+  </si>
+  <si>
+    <t>로우머</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A1%9C%EC%9A%B0%EB%A8%B8</t>
+  </si>
+  <si>
+    <t>6017억 4039만</t>
+  </si>
+  <si>
+    <t>떵헤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%96%B5%ED%97%A4</t>
+  </si>
+  <si>
+    <t>5809억 6317만</t>
+  </si>
+  <si>
+    <t>RIMS</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=RIMS</t>
+  </si>
+  <si>
+    <t>5483억 6978만</t>
+  </si>
+  <si>
+    <t>오말랑</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%A7%90%EB%9E%91</t>
+  </si>
+  <si>
+    <t>4763억 2057만</t>
+  </si>
+  <si>
+    <t>직불카드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%81%EB%B6%88%EC%B9%B4%EB%93%9C</t>
+  </si>
+  <si>
+    <t>1987억 6869만</t>
+  </si>
+  <si>
     <t>30</t>
-  </si>
-  <si>
-    <t>커피둥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%ED%94%BC%EB%91%A5</t>
-  </si>
-  <si>
-    <t>1119억 5831만</t>
-  </si>
-  <si>
-    <t>마퀸</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%ED%80%B8</t>
-  </si>
-  <si>
-    <t>39조 7974억 3406만</t>
-  </si>
-  <si>
-    <t>라면에계란탁</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EB%A9%B4%EC%97%90%EA%B3%84%EB%9E%80%ED%83%81</t>
-  </si>
-  <si>
-    <t>25조 8518억 9060만</t>
-  </si>
-  <si>
-    <t>에이비숍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EC%9D%B4%EB%B9%84%EC%88%8D</t>
-  </si>
-  <si>
-    <t>17조 4527억 529만</t>
-  </si>
-  <si>
-    <t>이금기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EA%B8%88%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>11조 3968억 6209만</t>
-  </si>
-  <si>
-    <t>환불카드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EB%B6%88%EC%B9%B4%EB%93%9C</t>
-  </si>
-  <si>
-    <t>7조 8198억 8819만</t>
-  </si>
-  <si>
-    <t>아빠카드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%B9%A0%EC%B9%B4%EB%93%9C</t>
-  </si>
-  <si>
-    <t>6조 1256억 7831만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%8F%84%EC%B9%B4%EB%93%9C</t>
-  </si>
-  <si>
-    <t>4조 1085억 3018만</t>
-  </si>
-  <si>
-    <t>시글</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EA%B8%80</t>
-  </si>
-  <si>
-    <t>4조 156억 2084만</t>
-  </si>
-  <si>
-    <t>공사과장</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EC%82%AC%EA%B3%BC%EC%9E%A5</t>
-  </si>
-  <si>
-    <t>1조 8947억 4945만</t>
-  </si>
-  <si>
-    <t>사과닷</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EA%B3%BC%EB%8B%B7</t>
-  </si>
-  <si>
-    <t>1조 7309억 6750만</t>
-  </si>
-  <si>
-    <t>토이감자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EC%9D%B4%EA%B0%90%EC%9E%90</t>
-  </si>
-  <si>
-    <t>1조 2864억 1536만</t>
-  </si>
-  <si>
-    <t>Eddy0825</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Eddy0825</t>
-  </si>
-  <si>
-    <t>1조 2641억 5580만</t>
-  </si>
-  <si>
-    <t>히히맘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%ED%9E%88%EB%A7%98</t>
-  </si>
-  <si>
-    <t>1조 1551억 3755만</t>
-  </si>
-  <si>
-    <t>망치전문</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%98%EC%A0%84%EB%AC%B8</t>
-  </si>
-  <si>
-    <t>1조 927억 6855만</t>
-  </si>
-  <si>
-    <t>핑와스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%91%EC%99%80%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>8953억 4884만</t>
-  </si>
-  <si>
-    <t>호츠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%B8%A0</t>
-  </si>
-  <si>
-    <t>8232억 647만</t>
-  </si>
-  <si>
-    <t>돌격대원</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EA%B2%A9%EB%8C%80%EC%9B%90</t>
-  </si>
-  <si>
-    <t>8183억 3301만</t>
-  </si>
-  <si>
-    <t>닉커</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%89%EC%BB%A4</t>
-  </si>
-  <si>
-    <t>8061억 7543만</t>
-  </si>
-  <si>
-    <t>비숍덩구</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%88%8D%EB%8D%A9%EA%B5%AC</t>
-  </si>
-  <si>
-    <t>7662억 1359만</t>
-  </si>
-  <si>
-    <t>단풍a</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8Da</t>
-  </si>
-  <si>
-    <t>7563억 4292만</t>
-  </si>
-  <si>
-    <t>문뚱식</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%9A%B1%EC%8B%9D</t>
-  </si>
-  <si>
-    <t>7185억 5363만</t>
-  </si>
-  <si>
-    <t>회원카드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9A%8C%EC%9B%90%EC%B9%B4%EB%93%9C</t>
-  </si>
-  <si>
-    <t>7126억 7783만</t>
-  </si>
-  <si>
-    <t>떼링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%96%BC%EB%A7%81</t>
-  </si>
-  <si>
-    <t>6842억 7643만</t>
-  </si>
-  <si>
-    <t>오보기다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%B3%B4%EA%B8%B0%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>6741억 7723만</t>
-  </si>
-  <si>
-    <t>로우머</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A1%9C%EC%9A%B0%EB%A8%B8</t>
-  </si>
-  <si>
-    <t>6017억 4039만</t>
-  </si>
-  <si>
-    <t>떵헤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%96%B5%ED%97%A4</t>
-  </si>
-  <si>
-    <t>5809억 6317만</t>
-  </si>
-  <si>
-    <t>RIMS</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=RIMS</t>
-  </si>
-  <si>
-    <t>5483억 6978만</t>
-  </si>
-  <si>
-    <t>오말랑</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%A7%90%EB%9E%91</t>
-  </si>
-  <si>
-    <t>4763억 2057만</t>
-  </si>
-  <si>
-    <t>직불카드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%81%EB%B6%88%EC%B9%B4%EB%93%9C</t>
-  </si>
-  <si>
-    <t>1987억 6869만</t>
   </si>
   <si>
     <t>채채자매</t>
@@ -3361,7 +3352,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -3810,10 +3801,10 @@
         <v>77</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>71</v>
+        <v>101</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>151</v>
+        <v>115</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>240</v>
@@ -3842,10 +3833,10 @@
         <v>77</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>115</v>
+        <v>151</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>243</v>
@@ -4194,13 +4185,13 @@
         <v>77</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>71</v>
+        <v>110</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -4214,22 +4205,22 @@
         <v>185</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>283</v>
@@ -4261,10 +4252,10 @@
         <v>71</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -4278,25 +4269,25 @@
         <v>194</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>71</v>
+        <v>290</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -4310,22 +4301,22 @@
         <v>198</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>293</v>
+        <v>90</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>295</v>
@@ -4334,40 +4325,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J31"/>
+  <autoFilter ref="A1:J30"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -4398,7 +4357,6 @@
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
     <hyperlink ref="E30" r:id="rId29"/>
-    <hyperlink ref="E31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4459,13 +4417,13 @@
         <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>77</v>
@@ -4477,7 +4435,7 @@
         <v>72</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -4491,13 +4449,13 @@
         <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>77</v>
@@ -4509,7 +4467,7 @@
         <v>96</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -4523,25 +4481,25 @@
         <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>79</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -4555,13 +4513,13 @@
         <v>87</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>77</v>
@@ -4573,7 +4531,7 @@
         <v>85</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -4587,13 +4545,13 @@
         <v>92</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>77</v>
@@ -4605,7 +4563,7 @@
         <v>151</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -4619,13 +4577,13 @@
         <v>98</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>77</v>
@@ -4637,7 +4595,7 @@
         <v>85</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -4657,7 +4615,7 @@
         <v>42</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>70</v>
@@ -4669,7 +4627,7 @@
         <v>85</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -4683,25 +4641,25 @@
         <v>107</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>85</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -4715,25 +4673,25 @@
         <v>112</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>146</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -4747,13 +4705,13 @@
         <v>117</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>77</v>
@@ -4765,7 +4723,7 @@
         <v>151</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -4779,13 +4737,13 @@
         <v>122</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>77</v>
@@ -4797,7 +4755,7 @@
         <v>146</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -4811,13 +4769,13 @@
         <v>126</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>77</v>
@@ -4829,7 +4787,7 @@
         <v>146</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -4843,13 +4801,13 @@
         <v>130</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>77</v>
@@ -4861,7 +4819,7 @@
         <v>146</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -4875,13 +4833,13 @@
         <v>134</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>77</v>
@@ -4893,7 +4851,7 @@
         <v>146</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -4907,13 +4865,13 @@
         <v>139</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>77</v>
@@ -4925,7 +4883,7 @@
         <v>146</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -4939,13 +4897,13 @@
         <v>143</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>77</v>
@@ -4957,7 +4915,7 @@
         <v>146</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -4971,13 +4929,13 @@
         <v>148</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>77</v>
@@ -4989,7 +4947,7 @@
         <v>252</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -5003,13 +4961,13 @@
         <v>153</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>77</v>
@@ -5021,7 +4979,7 @@
         <v>252</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -5035,13 +4993,13 @@
         <v>157</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>77</v>
@@ -5053,7 +5011,7 @@
         <v>137</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5067,13 +5025,13 @@
         <v>161</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>77</v>
@@ -5085,7 +5043,7 @@
         <v>146</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5099,13 +5057,13 @@
         <v>165</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>77</v>
@@ -5117,7 +5075,7 @@
         <v>146</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5131,13 +5089,13 @@
         <v>169</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>77</v>
@@ -5149,7 +5107,7 @@
         <v>265</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5163,13 +5121,13 @@
         <v>173</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>77</v>
@@ -5181,7 +5139,7 @@
         <v>265</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5195,13 +5153,13 @@
         <v>177</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>77</v>
@@ -5213,7 +5171,7 @@
         <v>146</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5227,13 +5185,13 @@
         <v>181</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>77</v>
@@ -5245,7 +5203,7 @@
         <v>146</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5259,13 +5217,13 @@
         <v>185</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>77</v>
@@ -5277,7 +5235,7 @@
         <v>265</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -5291,13 +5249,13 @@
         <v>190</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>77</v>
@@ -5309,7 +5267,7 @@
         <v>265</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -5323,13 +5281,13 @@
         <v>194</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>77</v>
@@ -5341,7 +5299,7 @@
         <v>265</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -5355,25 +5313,25 @@
         <v>198</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>275</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -5384,16 +5342,16 @@
         <v>33</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>296</v>
+        <v>382</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>77</v>
@@ -5402,10 +5360,10 @@
         <v>71</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -5504,13 +5462,13 @@
         <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>77</v>
@@ -5522,7 +5480,7 @@
         <v>85</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5536,13 +5494,13 @@
         <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>77</v>
@@ -5554,7 +5512,7 @@
         <v>85</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -5568,13 +5526,13 @@
         <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>77</v>
@@ -5586,7 +5544,7 @@
         <v>96</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -5600,13 +5558,13 @@
         <v>87</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>77</v>
@@ -5618,7 +5576,7 @@
         <v>85</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -5632,13 +5590,13 @@
         <v>92</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>77</v>
@@ -5650,7 +5608,7 @@
         <v>85</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -5664,13 +5622,13 @@
         <v>98</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>77</v>
@@ -5682,7 +5640,7 @@
         <v>85</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -5696,13 +5654,13 @@
         <v>103</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>77</v>
@@ -5714,7 +5672,7 @@
         <v>85</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -5728,13 +5686,13 @@
         <v>107</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>77</v>
@@ -5746,7 +5704,7 @@
         <v>85</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -5760,13 +5718,13 @@
         <v>112</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>77</v>
@@ -5778,7 +5736,7 @@
         <v>115</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -5792,13 +5750,13 @@
         <v>117</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>77</v>
@@ -5810,7 +5768,7 @@
         <v>115</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -5824,13 +5782,13 @@
         <v>122</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>77</v>
@@ -5842,7 +5800,7 @@
         <v>115</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5856,13 +5814,13 @@
         <v>126</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>77</v>
@@ -5874,7 +5832,7 @@
         <v>115</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5888,13 +5846,13 @@
         <v>130</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>77</v>
@@ -5906,7 +5864,7 @@
         <v>137</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -5920,13 +5878,13 @@
         <v>134</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>77</v>
@@ -5938,7 +5896,7 @@
         <v>252</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -5952,13 +5910,13 @@
         <v>139</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>77</v>
@@ -5970,7 +5928,7 @@
         <v>137</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5984,13 +5942,13 @@
         <v>143</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>77</v>
@@ -6002,7 +5960,7 @@
         <v>146</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -6016,13 +5974,13 @@
         <v>148</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>77</v>
@@ -6034,7 +5992,7 @@
         <v>151</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -6048,13 +6006,13 @@
         <v>153</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>77</v>
@@ -6066,7 +6024,7 @@
         <v>137</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -6080,13 +6038,13 @@
         <v>157</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>77</v>
@@ -6098,7 +6056,7 @@
         <v>146</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -6112,13 +6070,13 @@
         <v>161</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>77</v>
@@ -6130,7 +6088,7 @@
         <v>252</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -6144,13 +6102,13 @@
         <v>165</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>77</v>
@@ -6162,7 +6120,7 @@
         <v>252</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -6176,13 +6134,13 @@
         <v>169</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>77</v>
@@ -6194,7 +6152,7 @@
         <v>252</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -6208,13 +6166,13 @@
         <v>173</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>77</v>
@@ -6226,7 +6184,7 @@
         <v>252</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -6240,13 +6198,13 @@
         <v>177</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>77</v>
@@ -6258,7 +6216,7 @@
         <v>265</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -6278,7 +6236,7 @@
         <v>51</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>70</v>
@@ -6290,7 +6248,7 @@
         <v>265</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -6304,13 +6262,13 @@
         <v>185</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>77</v>
@@ -6322,7 +6280,7 @@
         <v>265</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -6336,13 +6294,13 @@
         <v>190</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>77</v>
@@ -6351,10 +6309,10 @@
         <v>78</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -6368,13 +6326,13 @@
         <v>194</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>77</v>
@@ -6386,7 +6344,7 @@
         <v>275</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -6400,13 +6358,13 @@
         <v>198</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>77</v>
@@ -6415,10 +6373,10 @@
         <v>90</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -6516,13 +6474,13 @@
         <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>77</v>
@@ -6534,7 +6492,7 @@
         <v>72</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -6554,7 +6512,7 @@
         <v>59</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>70</v>
@@ -6566,7 +6524,7 @@
         <v>72</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -6580,13 +6538,13 @@
         <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>77</v>
@@ -6598,7 +6556,7 @@
         <v>96</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -6612,13 +6570,13 @@
         <v>87</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>77</v>
@@ -6630,7 +6588,7 @@
         <v>85</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -6644,13 +6602,13 @@
         <v>92</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>77</v>
@@ -6662,7 +6620,7 @@
         <v>151</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -6676,13 +6634,13 @@
         <v>98</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>77</v>
@@ -6694,7 +6652,7 @@
         <v>151</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -6708,25 +6666,25 @@
         <v>103</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>137</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -6740,13 +6698,13 @@
         <v>107</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>77</v>
@@ -6758,7 +6716,7 @@
         <v>151</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -6772,13 +6730,13 @@
         <v>112</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>77</v>
@@ -6790,7 +6748,7 @@
         <v>146</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -6804,13 +6762,13 @@
         <v>117</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>77</v>
@@ -6822,7 +6780,7 @@
         <v>146</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -6836,13 +6794,13 @@
         <v>122</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>77</v>
@@ -6854,7 +6812,7 @@
         <v>137</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -6868,13 +6826,13 @@
         <v>126</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>77</v>
@@ -6886,7 +6844,7 @@
         <v>252</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -6900,13 +6858,13 @@
         <v>130</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>77</v>
@@ -6918,7 +6876,7 @@
         <v>252</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -6932,13 +6890,13 @@
         <v>134</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>77</v>
@@ -6950,7 +6908,7 @@
         <v>146</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -6964,13 +6922,13 @@
         <v>139</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>77</v>
@@ -6982,7 +6940,7 @@
         <v>146</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -6996,13 +6954,13 @@
         <v>143</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>77</v>
@@ -7014,7 +6972,7 @@
         <v>265</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -7028,13 +6986,13 @@
         <v>148</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>77</v>
@@ -7046,7 +7004,7 @@
         <v>275</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -7060,25 +7018,25 @@
         <v>153</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>252</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -7092,13 +7050,13 @@
         <v>157</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>77</v>
@@ -7110,7 +7068,7 @@
         <v>275</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -7124,13 +7082,13 @@
         <v>161</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>77</v>
@@ -7142,7 +7100,7 @@
         <v>265</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -7156,13 +7114,13 @@
         <v>165</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>77</v>
@@ -7174,7 +7132,7 @@
         <v>275</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -7188,13 +7146,13 @@
         <v>169</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>77</v>
@@ -7206,7 +7164,7 @@
         <v>275</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -7220,13 +7178,13 @@
         <v>173</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>77</v>
@@ -7238,7 +7196,7 @@
         <v>275</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -7252,13 +7210,13 @@
         <v>177</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>77</v>
@@ -7270,7 +7228,7 @@
         <v>275</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -7284,13 +7242,13 @@
         <v>181</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>77</v>
@@ -7299,10 +7257,10 @@
         <v>110</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -7316,25 +7274,25 @@
         <v>185</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -7348,13 +7306,13 @@
         <v>190</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>77</v>
@@ -7363,10 +7321,10 @@
         <v>78</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -7380,13 +7338,13 @@
         <v>194</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>77</v>
@@ -7395,10 +7353,10 @@
         <v>101</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>

--- a/reports/빅딜/빅딜_mgf_matched_5_guilds.xlsx
+++ b/reports/빅딜/빅딜_mgf_matched_5_guilds.xlsx
@@ -1577,7 +1577,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%96%80%EB%AC%BC%EA%B0%9C</t>
   </si>
   <si>
-    <t>5874억 4080만</t>
+    <t>5980억 8056만</t>
   </si>
   <si>
     <t>초코냥부하</t>
@@ -1667,7 +1667,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EA%B0%80%EB%82%9C%EA%BD%9D%EC%84%AD%EC%9D%B4</t>
   </si>
   <si>
-    <t>1713억 1425만</t>
+    <t>1715억 9218만</t>
   </si>
   <si>
     <t>이진니</t>

--- a/reports/빅딜/빅딜_mgf_matched_5_guilds.xlsx
+++ b/reports/빅딜/빅딜_mgf_matched_5_guilds.xlsx
@@ -10,16 +10,16 @@
     <sheet name="guilds" sheetId="1" r:id="rId1"/>
     <sheet name="빅딜" sheetId="2" r:id="rId2"/>
     <sheet name="피난민" sheetId="3" r:id="rId3"/>
-    <sheet name="이고이스트" sheetId="4" r:id="rId4"/>
-    <sheet name="부계둘" sheetId="5" r:id="rId5"/>
+    <sheet name="부계둘" sheetId="4" r:id="rId4"/>
+    <sheet name="이고이스트" sheetId="5" r:id="rId5"/>
     <sheet name="밤과다람쥐" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">밤과다람쥐!$A$1:$J$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">부계둘!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">부계둘!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">이고이스트!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">이고이스트!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">피난민!$A$1:$J$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -128,6 +128,33 @@
     <t>주방화</t>
   </si>
   <si>
+    <t>부계둘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B6%80%EA%B3%84%EB%91%98</t>
+  </si>
+  <si>
+    <t>Scania 29</t>
+  </si>
+  <si>
+    <t>378</t>
+  </si>
+  <si>
+    <t>10위</t>
+  </si>
+  <si>
+    <t>Lv.6</t>
+  </si>
+  <si>
+    <t>124조 4701억 3596만</t>
+  </si>
+  <si>
+    <t>부계들 + 부계둘</t>
+  </si>
+  <si>
+    <t>홍춘삼</t>
+  </si>
+  <si>
     <t>이고이스트</t>
   </si>
   <si>
@@ -158,33 +185,6 @@
     <t>한도카드</t>
   </si>
   <si>
-    <t>부계둘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B6%80%EA%B3%84%EB%91%98</t>
-  </si>
-  <si>
-    <t>Scania 29</t>
-  </si>
-  <si>
-    <t>378</t>
-  </si>
-  <si>
-    <t>10위</t>
-  </si>
-  <si>
-    <t>Lv.6</t>
-  </si>
-  <si>
-    <t>124조 4701억 3596만</t>
-  </si>
-  <si>
-    <t>부계들 + 부계둘</t>
-  </si>
-  <si>
-    <t>홍춘삼</t>
-  </si>
-  <si>
     <t>밤과다람쥐</t>
   </si>
   <si>
@@ -281,424 +281,424 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%AA%AC</t>
   </si>
   <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>12조 6365억 3160만</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>엘라임</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
+  </si>
+  <si>
+    <t>히어로</t>
+  </si>
+  <si>
+    <t>9조 2755억 5085만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>야가다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EA%B0%80%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>8조 7601억 85만</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>단풍카우</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EC%B9%B4%EC%9A%B0</t>
+  </si>
+  <si>
+    <t>7조 2379억 2599만</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>아르미느</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
+  </si>
+  <si>
+    <t>5조 9737억 2519만</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>포스코퓨처엠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EC%8A%A4%EC%BD%94%ED%93%A8%EC%B2%98%EC%97%A0</t>
+  </si>
+  <si>
+    <t>5조 1472억 5810만</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>굴러가는일상</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%B4%EB%9F%AC%EA%B0%80%EB%8A%94%EC%9D%BC%EC%83%81</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
+    <t>4조 8908억 6341만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>반도</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EB%8F%84</t>
+  </si>
+  <si>
+    <t>나이트로드</t>
+  </si>
+  <si>
+    <t>99</t>
+  </si>
+  <si>
+    <t>4조 4313억 1006만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>우후</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
+  </si>
+  <si>
+    <t>3조 5074억 2328만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>흑두부</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
+  </si>
+  <si>
+    <t>3조 3846억 5890만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>므고</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%80%EA%B3%A0</t>
+  </si>
+  <si>
+    <t>3조 144억 7218만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>비스밤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>2조 5343억 6737만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>아르젠타</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EC%A0%A0%ED%83%80</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>2조 4792억 2203만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>강철고튠데</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EC%B2%A0%EA%B3%A0%ED%8A%A0%EB%8D%B0</t>
+  </si>
+  <si>
+    <t>2조 4418억 6776만</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>꾸르꾸르</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A5%B4%EA%BE%B8%EB%A5%B4</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>2조 3765억 8123만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>민들레꽃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
+  </si>
+  <si>
+    <t>2조 3302억 2720만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>쭌파파</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%AD%8C%ED%8C%8C%ED%8C%8C</t>
+  </si>
+  <si>
+    <t>2조 854억 1372만</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>덕르코프</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8D%95%EB%A5%B4%EC%BD%94%ED%94%84</t>
+  </si>
+  <si>
+    <t>2조 575억 7597만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>여븨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%B8%A8</t>
+  </si>
+  <si>
+    <t>1조 9436억 1534만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>제스프리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EC%8A%A4%ED%94%84%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>1조 9311억 8518만</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>겨울바다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%A8%EC%9A%B8%EB%B0%94%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>1조 9074억 659만</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>플로우00</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%8C%EB%A1%9C%EC%9A%B000</t>
+  </si>
+  <si>
+    <t>1조 6923억 5834만</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>여눈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%88%88</t>
+  </si>
+  <si>
+    <t>1조 5909억 3493만</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>불보독지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EB%B3%B4%EB%8F%85%EC%A7%80</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>1조 5603억 9115만</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>데드캣</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8D%B0%EB%93%9C%EC%BA%A3</t>
+  </si>
+  <si>
+    <t>1조 5363억 9751만</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>욤지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A4%EC%A7%80</t>
+  </si>
+  <si>
+    <t>1조 2381억 1362만</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>혜영인기도1</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81%EC%9D%B8%EA%B8%B0%EB%8F%841</t>
+  </si>
+  <si>
+    <t>76</t>
+  </si>
+  <si>
+    <t>10억 3039만</t>
+  </si>
+  <si>
+    <t>샾한궁</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%ED%95%9C%EA%B6%81</t>
+  </si>
+  <si>
+    <t>27조 6316억 6311만</t>
+  </si>
+  <si>
+    <t>샾온</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%98%A8</t>
+  </si>
+  <si>
+    <t>20조 4459억 2037만</t>
+  </si>
+  <si>
+    <t>샾살개</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%82%B4%EA%B0%9C</t>
+  </si>
+  <si>
+    <t>17조 3578억 3768만</t>
+  </si>
+  <si>
+    <t>샾샷</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%83%B7</t>
+  </si>
+  <si>
+    <t>14조 7510억 2730만</t>
+  </si>
+  <si>
+    <t>고생했어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%83%9D%ED%96%88%EC%96%B4</t>
+  </si>
+  <si>
+    <t>9조 3382억 9591만</t>
+  </si>
+  <si>
+    <t>샾브샤브</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EB%B8%8C%EC%83%A4%EB%B8%8C</t>
+  </si>
+  <si>
+    <t>9조 1225억 1639만</t>
+  </si>
+  <si>
+    <t>샾밉당</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EB%B0%89%EB%8B%B9</t>
+  </si>
+  <si>
     <t>팔라딘</t>
   </si>
   <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>12조 6365억 3160만</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>엘라임</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
-  </si>
-  <si>
-    <t>히어로</t>
-  </si>
-  <si>
-    <t>9조 2650억 3725만</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>야가다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EA%B0%80%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>보우마스터</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>8조 7601억 85만</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>단풍카우</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EC%B9%B4%EC%9A%B0</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>7조 1872억 542만</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>아르미느</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
-  </si>
-  <si>
-    <t>5조 9165억 36만</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>굴러가는일상</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%B4%EB%9F%AC%EA%B0%80%EB%8A%94%EC%9D%BC%EC%83%81</t>
-  </si>
-  <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
-    <t>4조 8908억 6341만</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>포스코퓨처엠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EC%8A%A4%EC%BD%94%ED%93%A8%EC%B2%98%EC%97%A0</t>
-  </si>
-  <si>
-    <t>99</t>
-  </si>
-  <si>
-    <t>4조 8514억 8991만</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>반도</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EB%8F%84</t>
-  </si>
-  <si>
-    <t>나이트로드</t>
-  </si>
-  <si>
-    <t>3조 7623억 7295만</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>우후</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
-  </si>
-  <si>
-    <t>3조 4930억 3221만</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>흑두부</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
-  </si>
-  <si>
-    <t>3조 3846억 5890만</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>므고</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%80%EA%B3%A0</t>
-  </si>
-  <si>
-    <t>2조 8763억 3808만</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>비스밤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
-  </si>
-  <si>
-    <t>97</t>
-  </si>
-  <si>
-    <t>2조 5343억 6737만</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>강철고튠데</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EC%B2%A0%EA%B3%A0%ED%8A%A0%EB%8D%B0</t>
-  </si>
-  <si>
-    <t>2조 4418억 6776만</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>아르젠타</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EC%A0%A0%ED%83%80</t>
-  </si>
-  <si>
-    <t>96</t>
-  </si>
-  <si>
-    <t>2조 3773억 1331만</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>꾸르꾸르</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A5%B4%EA%BE%B8%EB%A5%B4</t>
-  </si>
-  <si>
-    <t>98</t>
-  </si>
-  <si>
-    <t>2조 3765억 8123만</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>민들레꽃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
-  </si>
-  <si>
-    <t>2조 3302억 2720만</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>쭌파파</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%AD%8C%ED%8C%8C%ED%8C%8C</t>
-  </si>
-  <si>
-    <t>2조 854억 1372만</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>덕르코프</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8D%95%EB%A5%B4%EC%BD%94%ED%94%84</t>
-  </si>
-  <si>
-    <t>2조 535억 4118만</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>여븨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%B8%A8</t>
-  </si>
-  <si>
-    <t>1조 9430억 2797만</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>제스프리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EC%8A%A4%ED%94%84%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>1조 9311억 8518만</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>겨울바다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%A8%EC%9A%B8%EB%B0%94%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>1조 7445억 1884만</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>플로우00</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%8C%EB%A1%9C%EC%9A%B000</t>
-  </si>
-  <si>
-    <t>1조 6923억 5834만</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>여눈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%88%88</t>
-  </si>
-  <si>
-    <t>1조 5909억 3493만</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>불보독지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EB%B3%B4%EB%8F%85%EC%A7%80</t>
-  </si>
-  <si>
-    <t>아크메이지(불,독)</t>
-  </si>
-  <si>
-    <t>1조 5603억 9115만</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>데드캣</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8D%B0%EB%93%9C%EC%BA%A3</t>
-  </si>
-  <si>
-    <t>1조 5363억 9751만</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>욤지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A4%EC%A7%80</t>
-  </si>
-  <si>
-    <t>1조 2381억 1362만</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>혜영인기도1</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81%EC%9D%B8%EA%B8%B0%EB%8F%841</t>
-  </si>
-  <si>
-    <t>75</t>
-  </si>
-  <si>
-    <t>10억 3039만</t>
-  </si>
-  <si>
-    <t>샾한궁</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%ED%95%9C%EA%B6%81</t>
-  </si>
-  <si>
-    <t>27조 6316억 6311만</t>
-  </si>
-  <si>
-    <t>샾온</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%98%A8</t>
-  </si>
-  <si>
-    <t>20조 4459억 2037만</t>
-  </si>
-  <si>
-    <t>샾살개</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%82%B4%EA%B0%9C</t>
-  </si>
-  <si>
-    <t>17조 3578억 3768만</t>
-  </si>
-  <si>
-    <t>샾샷</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%83%B7</t>
-  </si>
-  <si>
-    <t>14조 7510억 2730만</t>
-  </si>
-  <si>
-    <t>고생했어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%83%9D%ED%96%88%EC%96%B4</t>
-  </si>
-  <si>
-    <t>9조 3382억 9591만</t>
-  </si>
-  <si>
-    <t>샾브샤브</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EB%B8%8C%EC%83%A4%EB%B8%8C</t>
-  </si>
-  <si>
-    <t>8조 9948억 6426만</t>
-  </si>
-  <si>
-    <t>샾밉당</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EB%B0%89%EB%8B%B9</t>
-  </si>
-  <si>
-    <t>7조 7907억 4087만</t>
+    <t>8조 1605억 5099만</t>
   </si>
   <si>
     <t>샾꾸붕</t>
@@ -707,7 +707,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EA%BE%B8%EB%B6%95</t>
   </si>
   <si>
-    <t>4조 7062억 4091만</t>
+    <t>5조 4511억 8191만</t>
   </si>
   <si>
     <t>쩡미니지후</t>
@@ -734,31 +734,31 @@
     <t>2조 3354억 9574만</t>
   </si>
   <si>
+    <t>샾프심</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%ED%94%84%EC%8B%AC</t>
+  </si>
+  <si>
+    <t>2조 3158억 6653만</t>
+  </si>
+  <si>
+    <t>상산의조자룡</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EC%82%B0%EC%9D%98%EC%A1%B0%EC%9E%90%EB%A3%A1</t>
+  </si>
+  <si>
+    <t>2조 2158억 7896만</t>
+  </si>
+  <si>
     <t>샾오산</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%98%A4%EC%82%B0</t>
   </si>
   <si>
-    <t>2조 1548억 7397만</t>
-  </si>
-  <si>
-    <t>상산의조자룡</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EC%82%B0%EC%9D%98%EC%A1%B0%EC%9E%90%EB%A3%A1</t>
-  </si>
-  <si>
-    <t>2조 336억 4951만</t>
-  </si>
-  <si>
-    <t>샾프심</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%ED%94%84%EC%8B%AC</t>
-  </si>
-  <si>
-    <t>1조 9865억 8595만</t>
+    <t>2조 1574억 4420만</t>
   </si>
   <si>
     <t>김퍽퍽</t>
@@ -767,7 +767,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%8D%BD%ED%8D%BD</t>
   </si>
   <si>
-    <t>1조 7579억 7763만</t>
+    <t>1조 8756억 7377만</t>
   </si>
   <si>
     <t>샾감자</t>
@@ -785,18 +785,18 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%98%A4%ED%94%84</t>
   </si>
   <si>
+    <t>1조 5582억 599만</t>
+  </si>
+  <si>
+    <t>무진미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%A7%84%EB%AF%B8</t>
+  </si>
+  <si>
     <t>95</t>
   </si>
   <si>
-    <t>1조 3472억 5756만</t>
-  </si>
-  <si>
-    <t>무진미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%A7%84%EB%AF%B8</t>
-  </si>
-  <si>
     <t>1조 3439억 3411만</t>
   </si>
   <si>
@@ -806,7 +806,7 @@
     <t>https://mgf.gg/contents/character.php?n=oEMPo</t>
   </si>
   <si>
-    <t>1조 3260억 7678만</t>
+    <t>1조 3336억 5678만</t>
   </si>
   <si>
     <t>샾햇살</t>
@@ -836,7 +836,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%B1%EC%88%98%EB%8F%BC%EC%A7%80%EB%A1%9C%EC%84%B1</t>
   </si>
   <si>
-    <t>4736억 918만</t>
+    <t>4745억 6122만</t>
   </si>
   <si>
     <t>딱지냥</t>
@@ -845,7 +845,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%94%B1%EC%A7%80%EB%83%A5</t>
   </si>
   <si>
-    <t>3926억 8648만</t>
+    <t>4109억 2332만</t>
   </si>
   <si>
     <t>긩섷</t>
@@ -857,7 +857,7 @@
     <t>93</t>
   </si>
   <si>
-    <t>1822억 4872만</t>
+    <t>1864억 9941만</t>
   </si>
   <si>
     <t>샾갈배</t>
@@ -866,19 +866,19 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EA%B0%88%EB%B0%B0</t>
   </si>
   <si>
+    <t>1673억 5338만</t>
+  </si>
+  <si>
+    <t>샾앤플랫</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%95%A4%ED%94%8C%EB%9E%AB</t>
+  </si>
+  <si>
     <t>92</t>
   </si>
   <si>
-    <t>1594억 5386만</t>
-  </si>
-  <si>
-    <t>샾앤플랫</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%95%A4%ED%94%8C%EB%9E%AB</t>
-  </si>
-  <si>
-    <t>1575억 9253만</t>
+    <t>1582억 4444만</t>
   </si>
   <si>
     <t>최훈석개멋져</t>
@@ -890,7 +890,7 @@
     <t>90</t>
   </si>
   <si>
-    <t>1306억 1455만</t>
+    <t>1450억 7248만</t>
   </si>
   <si>
     <t>샾사니서리당</t>
@@ -905,7 +905,7 @@
     <t>91</t>
   </si>
   <si>
-    <t>1283억 4276만</t>
+    <t>1284억 6855만</t>
   </si>
   <si>
     <t>커피둥</t>
@@ -917,13 +917,286 @@
     <t>1119억 5831만</t>
   </si>
   <si>
+    <t>가온스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%98%A8%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>17조 3732억 4655만</t>
+  </si>
+  <si>
+    <t>둥둥콩이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%91%A5%EB%91%A5%EC%BD%A9%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>16조 4186억 1612만</t>
+  </si>
+  <si>
+    <t>증권보이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A6%9D%EA%B6%8C%EB%B3%B4%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>12조 68억 2568만</t>
+  </si>
+  <si>
+    <t>Canary</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Canary</t>
+  </si>
+  <si>
+    <t>11조 5009억 9607만</t>
+  </si>
+  <si>
+    <t>처히</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%98%ED%9E%88</t>
+  </si>
+  <si>
+    <t>9조 7554억 7539만</t>
+  </si>
+  <si>
+    <t>환생의불꼬츠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EC%83%9D%EC%9D%98%EB%B6%88%EA%BC%AC%EC%B8%A0</t>
+  </si>
+  <si>
+    <t>9조 2454억 5199만</t>
+  </si>
+  <si>
+    <t>밍진</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%8D%EC%A7%84</t>
+  </si>
+  <si>
+    <t>8조 9166억 6911만</t>
+  </si>
+  <si>
+    <t>Naco</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Naco</t>
+  </si>
+  <si>
+    <t>6조 7523억 5853만</t>
+  </si>
+  <si>
+    <t>AKPS</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=AKPS</t>
+  </si>
+  <si>
+    <t>5조 644억 4933만</t>
+  </si>
+  <si>
+    <t>로베르트슈만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A1%9C%EB%B2%A0%EB%A5%B4%ED%8A%B8%EC%8A%88%EB%A7%8C</t>
+  </si>
+  <si>
+    <t>4조 6954억 1280만</t>
+  </si>
+  <si>
+    <t>사나이기백황</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%82%98%EC%9D%B4%EA%B8%B0%EB%B0%B1%ED%99%A9</t>
+  </si>
+  <si>
+    <t>3조 4297억 6701만</t>
+  </si>
+  <si>
+    <t>천칠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%B9%A0</t>
+  </si>
+  <si>
+    <t>2조 6702억 2482만</t>
+  </si>
+  <si>
+    <t>평평이형</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%89%ED%8F%89%EC%9D%B4%ED%98%95</t>
+  </si>
+  <si>
+    <t>2조 6657억 7512만</t>
+  </si>
+  <si>
+    <t>토니워터</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%8B%88%EC%9B%8C%ED%84%B0</t>
+  </si>
+  <si>
+    <t>2조 6162억 1545만</t>
+  </si>
+  <si>
+    <t>토미오카상</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%AF%B8%EC%98%A4%EC%B9%B4%EC%83%81</t>
+  </si>
+  <si>
+    <t>2조 5413억 4660만</t>
+  </si>
+  <si>
+    <t>화살대</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%82%B4%EB%8C%80</t>
+  </si>
+  <si>
+    <t>2조 1638억 2188만</t>
+  </si>
+  <si>
+    <t>런닝래빗</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9F%B0%EB%8B%9D%EB%9E%98%EB%B9%97</t>
+  </si>
+  <si>
+    <t>1조 9922억 3298만</t>
+  </si>
+  <si>
+    <t>펑풀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8E%91%ED%92%80</t>
+  </si>
+  <si>
+    <t>1조 9394억 7225만</t>
+  </si>
+  <si>
+    <t>피어난</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%BC%EC%96%B4%EB%82%9C</t>
+  </si>
+  <si>
+    <t>1조 6873억 4877만</t>
+  </si>
+  <si>
+    <t>샤스찌에</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%A4%EC%8A%A4%EC%B0%8C%EC%97%90</t>
+  </si>
+  <si>
+    <t>1조 1555억 4960만</t>
+  </si>
+  <si>
+    <t>지니좋아요</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EB%8B%88%EC%A2%8B%EC%95%84%EC%9A%94</t>
+  </si>
+  <si>
+    <t>1조 348억 601만</t>
+  </si>
+  <si>
+    <t>보동핑</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%8F%99%ED%95%91</t>
+  </si>
+  <si>
+    <t>1조 167억 2526만</t>
+  </si>
+  <si>
+    <t>싸토루</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B8%ED%86%A0%EB%A3%A8</t>
+  </si>
+  <si>
+    <t>9713억 8758만</t>
+  </si>
+  <si>
+    <t>2026년1월30일</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=2026%EB%85%841%EC%9B%9430%EC%9D%BC</t>
+  </si>
+  <si>
+    <t>7424억 6962만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%8D%EC%B6%98%EC%82%BC</t>
+  </si>
+  <si>
+    <t>7170억 1216만</t>
+  </si>
+  <si>
+    <t>찐곽정근</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B0%90%EA%B3%BD%EC%A0%95%EA%B7%BC</t>
+  </si>
+  <si>
+    <t>7074억 9433만</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Targa</t>
+  </si>
+  <si>
+    <t>5665억 5826만</t>
+  </si>
+  <si>
+    <t>애둘이에요</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%A0%EB%91%98%EC%9D%B4%EC%97%90%EC%9A%94</t>
+  </si>
+  <si>
+    <t>5120억 6458만</t>
+  </si>
+  <si>
+    <t>짱창훈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%B1%EC%B0%BD%ED%9B%88</t>
+  </si>
+  <si>
+    <t>2730억 2959만</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>구리구리뽕리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%A6%AC%EA%B5%AC%EB%A6%AC%EB%BD%95%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>51억 9387만</t>
+  </si>
+  <si>
     <t>마퀸</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%ED%80%B8</t>
   </si>
   <si>
-    <t>39조 7974억 3406만</t>
+    <t>41조 8046억 1469만</t>
   </si>
   <si>
     <t>라면에계란탁</t>
@@ -932,7 +1205,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EB%A9%B4%EC%97%90%EA%B3%84%EB%9E%80%ED%83%81</t>
   </si>
   <si>
-    <t>25조 8518억 9060만</t>
+    <t>27조 944억 9823만</t>
   </si>
   <si>
     <t>에이비숍</t>
@@ -944,22 +1217,13 @@
     <t>17조 4527억 529만</t>
   </si>
   <si>
-    <t>이금기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EA%B8%88%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>11조 3968억 6209만</t>
-  </si>
-  <si>
     <t>환불카드</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EB%B6%88%EC%B9%B4%EB%93%9C</t>
   </si>
   <si>
-    <t>7조 8198억 8819만</t>
+    <t>10조 6115억 767만</t>
   </si>
   <si>
     <t>아빠카드</t>
@@ -968,13 +1232,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%B9%A0%EC%B9%B4%EB%93%9C</t>
   </si>
   <si>
-    <t>6조 1256억 7831만</t>
+    <t>6조 2555억 5372만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%8F%84%EC%B9%B4%EB%93%9C</t>
   </si>
   <si>
-    <t>4조 3123억 341만</t>
+    <t>4조 5600억 4692만</t>
   </si>
   <si>
     <t>시글</t>
@@ -992,7 +1256,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EC%82%AC%EA%B3%BC%EC%9E%A5</t>
   </si>
   <si>
-    <t>1조 8947억 4945만</t>
+    <t>2조 4059억 2866만</t>
   </si>
   <si>
     <t>사과닷</t>
@@ -1001,7 +1265,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EA%B3%BC%EB%8B%B7</t>
   </si>
   <si>
-    <t>1조 7309억 6750만</t>
+    <t>1조 9505억 2596만</t>
   </si>
   <si>
     <t>토이감자</t>
@@ -1010,7 +1274,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EC%9D%B4%EA%B0%90%EC%9E%90</t>
   </si>
   <si>
-    <t>1조 2864억 1536만</t>
+    <t>1조 3297억 1328만</t>
   </si>
   <si>
     <t>Eddy0825</t>
@@ -1019,7 +1283,7 @@
     <t>https://mgf.gg/contents/character.php?n=Eddy0825</t>
   </si>
   <si>
-    <t>1조 2641억 5580만</t>
+    <t>1조 2699억 1720만</t>
   </si>
   <si>
     <t>히히맘</t>
@@ -1028,7 +1292,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%ED%9E%88%EB%A7%98</t>
   </si>
   <si>
-    <t>1조 1551억 3755만</t>
+    <t>1조 1570억 1834만</t>
   </si>
   <si>
     <t>망치전문</t>
@@ -1037,7 +1301,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%98%EC%A0%84%EB%AC%B8</t>
   </si>
   <si>
-    <t>1조 927억 6855만</t>
+    <t>1조 946억 7036만</t>
   </si>
   <si>
     <t>핑와스</t>
@@ -1055,7 +1319,25 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%B8%A0</t>
   </si>
   <si>
-    <t>8232억 647만</t>
+    <t>8817억 1133만</t>
+  </si>
+  <si>
+    <t>비숍덩구</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%88%8D%EB%8D%A9%EA%B5%AC</t>
+  </si>
+  <si>
+    <t>8325억 778만</t>
+  </si>
+  <si>
+    <t>닉커</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%89%EC%BB%A4</t>
+  </si>
+  <si>
+    <t>8229억 2581만</t>
   </si>
   <si>
     <t>돌격대원</t>
@@ -1067,22 +1349,13 @@
     <t>8183억 3301만</t>
   </si>
   <si>
-    <t>닉커</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%89%EC%BB%A4</t>
-  </si>
-  <si>
-    <t>8061억 7543만</t>
-  </si>
-  <si>
-    <t>비숍덩구</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%88%8D%EB%8D%A9%EA%B5%AC</t>
-  </si>
-  <si>
-    <t>7662억 1359만</t>
+    <t>문뚱식</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%9A%B1%EC%8B%9D</t>
+  </si>
+  <si>
+    <t>8138억 1022만</t>
   </si>
   <si>
     <t>단풍a</t>
@@ -1091,16 +1364,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8Da</t>
   </si>
   <si>
-    <t>7563억 4292만</t>
-  </si>
-  <si>
-    <t>문뚱식</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%9A%B1%EC%8B%9D</t>
-  </si>
-  <si>
-    <t>7185억 5363만</t>
+    <t>8039억 8999만</t>
   </si>
   <si>
     <t>회원카드</t>
@@ -1118,7 +1382,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%96%BC%EB%A7%81</t>
   </si>
   <si>
-    <t>6972억 1001만</t>
+    <t>7062억 4172만</t>
   </si>
   <si>
     <t>오보기다</t>
@@ -1136,7 +1400,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A1%9C%EC%9A%B0%EB%A8%B8</t>
   </si>
   <si>
-    <t>6017억 4039만</t>
+    <t>6583억 4222만</t>
+  </si>
+  <si>
+    <t>RIMS</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=RIMS</t>
+  </si>
+  <si>
+    <t>5821억 9350만</t>
   </si>
   <si>
     <t>떵헤</t>
@@ -1148,15 +1421,6 @@
     <t>5809억 6317만</t>
   </si>
   <si>
-    <t>RIMS</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=RIMS</t>
-  </si>
-  <si>
-    <t>5483억 6978만</t>
-  </si>
-  <si>
     <t>오말랑</t>
   </si>
   <si>
@@ -1172,10 +1436,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%81%EB%B6%88%EC%B9%B4%EB%93%9C</t>
   </si>
   <si>
-    <t>1987억 6869만</t>
-  </si>
-  <si>
-    <t>30</t>
+    <t>2112억 3447만</t>
   </si>
   <si>
     <t>채채자매</t>
@@ -1184,268 +1445,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EC%B1%84%EC%9E%90%EB%A7%A4</t>
   </si>
   <si>
-    <t>1126억 3775만</t>
-  </si>
-  <si>
-    <t>가온스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%98%A8%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>17조 777억 7587만</t>
-  </si>
-  <si>
-    <t>둥둥콩이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%91%A5%EB%91%A5%EC%BD%A9%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>16조 299억 2014만</t>
-  </si>
-  <si>
-    <t>증권보이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A6%9D%EA%B6%8C%EB%B3%B4%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>12조 68억 2568만</t>
-  </si>
-  <si>
-    <t>Canary</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Canary</t>
-  </si>
-  <si>
-    <t>11조 5009억 9607만</t>
-  </si>
-  <si>
-    <t>처히</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%98%ED%9E%88</t>
-  </si>
-  <si>
-    <t>9조 3407억 8283만</t>
-  </si>
-  <si>
-    <t>환생의불꼬츠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EC%83%9D%EC%9D%98%EB%B6%88%EA%BC%AC%EC%B8%A0</t>
-  </si>
-  <si>
-    <t>9조 2454억 5199만</t>
-  </si>
-  <si>
-    <t>밍진</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%8D%EC%A7%84</t>
-  </si>
-  <si>
-    <t>8조 9166억 6911만</t>
-  </si>
-  <si>
-    <t>Naco</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Naco</t>
-  </si>
-  <si>
-    <t>6조 6735억 7182만</t>
-  </si>
-  <si>
-    <t>AKPS</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=AKPS</t>
-  </si>
-  <si>
-    <t>4조 8996억 3708만</t>
-  </si>
-  <si>
-    <t>로베르트슈만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A1%9C%EB%B2%A0%EB%A5%B4%ED%8A%B8%EC%8A%88%EB%A7%8C</t>
-  </si>
-  <si>
-    <t>3조 9701억 9740만</t>
-  </si>
-  <si>
-    <t>사나이기백황</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%82%98%EC%9D%B4%EA%B8%B0%EB%B0%B1%ED%99%A9</t>
-  </si>
-  <si>
-    <t>3조 4240억 573만</t>
-  </si>
-  <si>
-    <t>천칠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%B9%A0</t>
-  </si>
-  <si>
-    <t>2조 6405억 2496만</t>
-  </si>
-  <si>
-    <t>토미오카상</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%AF%B8%EC%98%A4%EC%B9%B4%EC%83%81</t>
-  </si>
-  <si>
-    <t>2조 5102억 2762만</t>
-  </si>
-  <si>
-    <t>평평이형</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%89%ED%8F%89%EC%9D%B4%ED%98%95</t>
-  </si>
-  <si>
-    <t>2조 4065억 7040만</t>
-  </si>
-  <si>
-    <t>토니워터</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%8B%88%EC%9B%8C%ED%84%B0</t>
-  </si>
-  <si>
-    <t>2조 1861억 3135만</t>
-  </si>
-  <si>
-    <t>런닝래빗</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9F%B0%EB%8B%9D%EB%9E%98%EB%B9%97</t>
-  </si>
-  <si>
-    <t>1조 9922억 3298만</t>
-  </si>
-  <si>
-    <t>화살대</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%82%B4%EB%8C%80</t>
-  </si>
-  <si>
-    <t>1조 9701억 2021만</t>
-  </si>
-  <si>
-    <t>피어난</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%BC%EC%96%B4%EB%82%9C</t>
-  </si>
-  <si>
-    <t>1조 6873억 4877만</t>
-  </si>
-  <si>
-    <t>펑풀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8E%91%ED%92%80</t>
-  </si>
-  <si>
-    <t>1조 6522억 7711만</t>
-  </si>
-  <si>
-    <t>샤스찌에</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%A4%EC%8A%A4%EC%B0%8C%EC%97%90</t>
-  </si>
-  <si>
-    <t>1조 1338억 4251만</t>
-  </si>
-  <si>
-    <t>싸토루</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B8%ED%86%A0%EB%A3%A8</t>
-  </si>
-  <si>
-    <t>9581억 2612만</t>
-  </si>
-  <si>
-    <t>보동핑</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%8F%99%ED%95%91</t>
-  </si>
-  <si>
-    <t>9446억 2849만</t>
-  </si>
-  <si>
-    <t>2026년1월30일</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=2026%EB%85%841%EC%9B%9430%EC%9D%BC</t>
-  </si>
-  <si>
-    <t>7424억 6962만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%8D%EC%B6%98%EC%82%BC</t>
-  </si>
-  <si>
-    <t>7170억 1216만</t>
-  </si>
-  <si>
-    <t>찐곽정근</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B0%90%EA%B3%BD%EC%A0%95%EA%B7%BC</t>
-  </si>
-  <si>
-    <t>7074억 9433만</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Targa</t>
-  </si>
-  <si>
-    <t>5246억 1786만</t>
-  </si>
-  <si>
-    <t>애둘이에요</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%A0%EB%91%98%EC%9D%B4%EC%97%90%EC%9A%94</t>
-  </si>
-  <si>
-    <t>5054억 4801만</t>
-  </si>
-  <si>
-    <t>짱창훈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%B1%EC%B0%BD%ED%9B%88</t>
-  </si>
-  <si>
-    <t>2635억 4225만</t>
-  </si>
-  <si>
-    <t>구리구리뽕리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%A6%AC%EA%B5%AC%EB%A6%AC%EB%BD%95%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>80</t>
-  </si>
-  <si>
-    <t>51억 9387만</t>
+    <t>1361억 398만</t>
   </si>
   <si>
     <t>MAKTO</t>
@@ -1454,13 +1454,13 @@
     <t>https://mgf.gg/contents/character.php?n=MAKTO</t>
   </si>
   <si>
-    <t>84조 1898억 3942만</t>
+    <t>87조 9937억 4731만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EB%AF%B8%ED%98%95</t>
   </si>
   <si>
-    <t>47조 8894억 2761만</t>
+    <t>50조 3315억 1281만</t>
   </si>
   <si>
     <t>민헤</t>
@@ -1505,7 +1505,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B1%B4%EC%95%BC%EC%9B%85</t>
   </si>
   <si>
-    <t>1조 9230억 4486만</t>
+    <t>1조 9254억 7512만</t>
   </si>
   <si>
     <t>보꿍</t>
@@ -1523,7 +1523,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EB%85%84%EA%B0%80%EC%9E%A5%EC%9B%90%EB%94%9C</t>
   </si>
   <si>
-    <t>1조 2928억 7910만</t>
+    <t>1조 3553억 3451만</t>
   </si>
   <si>
     <t>치킨v</t>
@@ -1532,7 +1532,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B9%98%ED%82%A8v</t>
   </si>
   <si>
-    <t>1조 1165억 62만</t>
+    <t>1조 1922억 5473만</t>
   </si>
   <si>
     <t>레제내꺼야</t>
@@ -1541,7 +1541,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A0%88%EC%A0%9C%EB%82%B4%EA%BA%BC%EC%95%BC</t>
   </si>
   <si>
-    <t>8606억 4124만</t>
+    <t>8961억 5267만</t>
   </si>
   <si>
     <t>키죠</t>
@@ -1568,7 +1568,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%A8%EB%B0%8D</t>
   </si>
   <si>
-    <t>7357억 4366만</t>
+    <t>7618억 2362만</t>
   </si>
   <si>
     <t>하얀물개</t>
@@ -1577,7 +1577,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%96%80%EB%AC%BC%EA%B0%9C</t>
   </si>
   <si>
-    <t>5980억 8056만</t>
+    <t>6229억 7916만</t>
   </si>
   <si>
     <t>초코냥부하</t>
@@ -1586,7 +1586,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%BD%94%EB%83%A5%EB%B6%80%ED%95%98</t>
   </si>
   <si>
-    <t>5488억 3441만</t>
+    <t>5556억 6668만</t>
   </si>
   <si>
     <t>장빵구</t>
@@ -1595,7 +1595,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EB%B9%B5%EA%B5%AC</t>
   </si>
   <si>
-    <t>5324억 8670만</t>
+    <t>5419억 8997만</t>
   </si>
   <si>
     <t>레피스나2</t>
@@ -1613,7 +1613,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EB%B6%88%EB%83%A0%EB%83%A0</t>
   </si>
   <si>
-    <t>4342억 5207만</t>
+    <t>4596억 3206만</t>
   </si>
   <si>
     <t>혼자가최고</t>
@@ -1622,7 +1622,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%BC%EC%9E%90%EA%B0%80%EC%B5%9C%EA%B3%A0</t>
   </si>
   <si>
-    <t>4288억 7300만</t>
+    <t>4346억 9012만</t>
   </si>
   <si>
     <t>깝용잉</t>
@@ -1640,7 +1640,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EB%B3%B5%EB%B3%B5</t>
   </si>
   <si>
-    <t>3570억 2887만</t>
+    <t>3742억 3818만</t>
   </si>
   <si>
     <t>모몬쌍</t>
@@ -1649,7 +1649,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EB%AA%AC%EC%8C%8D</t>
   </si>
   <si>
-    <t>2258억 9094만</t>
+    <t>2440억 7917만</t>
   </si>
   <si>
     <t>우주강아지</t>
@@ -1667,7 +1667,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EA%B0%80%EB%82%9C%EA%BD%9D%EC%84%AD%EC%9D%B4</t>
   </si>
   <si>
-    <t>1715억 9218만</t>
+    <t>1719억 3297만</t>
   </si>
   <si>
     <t>이진니</t>
@@ -1676,7 +1676,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%A7%84%EB%8B%88</t>
   </si>
   <si>
-    <t>787억 4435만</t>
+    <t>847억 1891만</t>
   </si>
   <si>
     <t>봉오리</t>
@@ -1688,7 +1688,7 @@
     <t>86</t>
   </si>
   <si>
-    <t>647억 8326만</t>
+    <t>681억 6134만</t>
   </si>
   <si>
     <t>만년설딸기</t>
@@ -1697,10 +1697,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%8C%EB%85%84%EC%84%A4%EB%94%B8%EA%B8%B0</t>
   </si>
   <si>
-    <t>83</t>
-  </si>
-  <si>
-    <t>131억 9115만</t>
+    <t>84</t>
+  </si>
+  <si>
+    <t>193억 122만</t>
   </si>
 </sst>
 </file>
@@ -2228,16 +2228,16 @@
         <v>38</v>
       </c>
       <c r="I4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>24</v>
@@ -2245,31 +2245,31 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="C5" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>49</v>
@@ -2307,7 +2307,7 @@
         <v>18</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>56</v>
@@ -2565,13 +2565,13 @@
         <v>77</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>79</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -2582,16 +2582,16 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>105</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>77</v>
@@ -2600,10 +2600,10 @@
         <v>90</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -2614,28 +2614,28 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>109</v>
-      </c>
       <c r="F9" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>85</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -2646,28 +2646,28 @@
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="H10" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>116</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -2678,28 +2678,28 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="H11" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G11" s="2" t="s">
+      <c r="I11" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>121</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -2710,16 +2710,16 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>124</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>77</v>
@@ -2728,10 +2728,10 @@
         <v>90</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -2742,28 +2742,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>129</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -2774,16 +2774,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>131</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>132</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>77</v>
@@ -2795,7 +2795,7 @@
         <v>85</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -2806,28 +2806,28 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H15" s="2" t="s">
+      <c r="I15" s="2" t="s">
         <v>137</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>138</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -2838,25 +2838,25 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>115</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>142</v>
@@ -2885,13 +2885,13 @@
         <v>77</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="H17" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>147</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -2902,16 +2902,16 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>149</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>150</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>77</v>
@@ -2920,10 +2920,10 @@
         <v>71</v>
       </c>
       <c r="H18" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>152</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -2934,28 +2934,28 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>155</v>
-      </c>
       <c r="F19" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>85</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -2966,16 +2966,16 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>158</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>159</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>77</v>
@@ -2984,10 +2984,10 @@
         <v>71</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -2998,16 +2998,16 @@
         <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="D21" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>162</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>163</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>77</v>
@@ -3016,10 +3016,10 @@
         <v>71</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3030,16 +3030,16 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>77</v>
@@ -3051,7 +3051,7 @@
         <v>85</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3062,16 +3062,16 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="D23" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>170</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>171</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>77</v>
@@ -3080,10 +3080,10 @@
         <v>78</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3094,28 +3094,28 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="D24" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>175</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>176</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3126,16 +3126,16 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="D25" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>179</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>77</v>
@@ -3144,10 +3144,10 @@
         <v>95</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3158,16 +3158,16 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="D26" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>183</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>77</v>
@@ -3176,10 +3176,10 @@
         <v>71</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -3190,28 +3190,28 @@
         <v>13</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="D27" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G27" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="F27" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G27" s="2" t="s">
+      <c r="H27" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>189</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3222,16 +3222,16 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="D28" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>192</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>77</v>
@@ -3240,10 +3240,10 @@
         <v>78</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3254,16 +3254,16 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="D29" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>195</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>196</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>77</v>
@@ -3272,10 +3272,10 @@
         <v>71</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -3286,16 +3286,16 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="D30" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>199</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>200</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>77</v>
@@ -3304,10 +3304,10 @@
         <v>71</v>
       </c>
       <c r="H30" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>201</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>202</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -3405,13 +3405,13 @@
         <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>77</v>
@@ -3420,10 +3420,10 @@
         <v>78</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -3437,13 +3437,13 @@
         <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>207</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>77</v>
@@ -3455,7 +3455,7 @@
         <v>96</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -3469,13 +3469,13 @@
         <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>209</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>77</v>
@@ -3487,7 +3487,7 @@
         <v>96</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -3501,13 +3501,13 @@
         <v>87</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>212</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>213</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>77</v>
@@ -3519,7 +3519,7 @@
         <v>85</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -3533,25 +3533,25 @@
         <v>92</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>216</v>
-      </c>
       <c r="F6" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>85</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -3565,25 +3565,25 @@
         <v>98</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>219</v>
-      </c>
       <c r="F7" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>85</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -3594,22 +3594,22 @@
         <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>222</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>84</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>96</v>
@@ -3626,7 +3626,7 @@
         <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>224</v>
@@ -3644,7 +3644,7 @@
         <v>90</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>226</v>
@@ -3658,7 +3658,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>227</v>
@@ -3673,10 +3673,10 @@
         <v>77</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>229</v>
@@ -3690,7 +3690,7 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>230</v>
@@ -3708,7 +3708,7 @@
         <v>71</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>232</v>
@@ -3722,7 +3722,7 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>32</v>
@@ -3740,7 +3740,7 @@
         <v>90</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>234</v>
@@ -3754,7 +3754,7 @@
         <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>235</v>
@@ -3772,7 +3772,7 @@
         <v>71</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>237</v>
@@ -3786,7 +3786,7 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>238</v>
@@ -3801,10 +3801,10 @@
         <v>77</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>240</v>
@@ -3818,7 +3818,7 @@
         <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>241</v>
@@ -3836,7 +3836,7 @@
         <v>71</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>243</v>
@@ -3850,7 +3850,7 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>244</v>
@@ -3865,7 +3865,7 @@
         <v>77</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>85</v>
@@ -3897,10 +3897,10 @@
         <v>77</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>249</v>
@@ -3914,7 +3914,7 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>250</v>
@@ -3929,13 +3929,13 @@
         <v>77</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="H18" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>252</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>253</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -3946,16 +3946,16 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>254</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>255</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>77</v>
@@ -3964,7 +3964,7 @@
         <v>71</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>256</v>
@@ -3978,7 +3978,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>257</v>
@@ -3993,10 +3993,10 @@
         <v>77</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>259</v>
@@ -4010,7 +4010,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>260</v>
@@ -4025,10 +4025,10 @@
         <v>77</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>262</v>
@@ -4042,7 +4042,7 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>263</v>
@@ -4074,7 +4074,7 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>267</v>
@@ -4089,7 +4089,7 @@
         <v>77</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>265</v>
@@ -4106,7 +4106,7 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>270</v>
@@ -4121,7 +4121,7 @@
         <v>77</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>265</v>
@@ -4138,7 +4138,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>273</v>
@@ -4170,7 +4170,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>277</v>
@@ -4185,13 +4185,13 @@
         <v>77</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="H26" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>279</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>280</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -4202,16 +4202,16 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>281</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>282</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>77</v>
@@ -4220,7 +4220,7 @@
         <v>71</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>283</v>
@@ -4234,7 +4234,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>284</v>
@@ -4266,7 +4266,7 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>288</v>
@@ -4298,7 +4298,7 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>293</v>
@@ -4316,7 +4316,7 @@
         <v>90</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>295</v>
@@ -4429,10 +4429,10 @@
         <v>77</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>298</v>
@@ -4461,7 +4461,7 @@
         <v>77</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>96</v>
@@ -4493,10 +4493,10 @@
         <v>77</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>290</v>
+        <v>71</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>304</v>
@@ -4557,10 +4557,10 @@
         <v>77</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>151</v>
+        <v>85</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>310</v>
@@ -4589,7 +4589,7 @@
         <v>77</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>85</v>
@@ -4606,19 +4606,19 @@
         <v>33</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>42</v>
+        <v>314</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>42</v>
+        <v>314</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>71</v>
@@ -4627,7 +4627,7 @@
         <v>85</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -4638,28 +4638,28 @@
         <v>33</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>290</v>
+        <v>113</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>85</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -4670,28 +4670,28 @@
         <v>33</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>290</v>
+        <v>84</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>146</v>
+        <v>119</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -4702,28 +4702,28 @@
         <v>33</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>151</v>
+        <v>119</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -4734,28 +4734,28 @@
         <v>33</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>146</v>
+        <v>119</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -4766,28 +4766,28 @@
         <v>33</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>78</v>
+        <v>222</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>146</v>
+        <v>119</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -4798,28 +4798,28 @@
         <v>33</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -4830,28 +4830,28 @@
         <v>33</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -4862,28 +4862,28 @@
         <v>33</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -4897,25 +4897,25 @@
         <v>143</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -4926,28 +4926,28 @@
         <v>33</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>252</v>
+        <v>141</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -4958,28 +4958,28 @@
         <v>33</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>252</v>
+        <v>141</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -4990,28 +4990,28 @@
         <v>33</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5022,28 +5022,28 @@
         <v>33</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>146</v>
+        <v>255</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5054,16 +5054,16 @@
         <v>33</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>77</v>
@@ -5072,10 +5072,10 @@
         <v>71</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5086,28 +5086,28 @@
         <v>33</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>265</v>
+        <v>141</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5118,28 +5118,28 @@
         <v>33</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>110</v>
+        <v>84</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5150,28 +5150,28 @@
         <v>33</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>71</v>
+        <v>113</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5182,25 +5182,25 @@
         <v>33</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>367</v>
+        <v>41</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>367</v>
+        <v>41</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>368</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>146</v>
+        <v>265</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>369</v>
@@ -5214,7 +5214,7 @@
         <v>33</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>370</v>
@@ -5229,7 +5229,7 @@
         <v>77</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>110</v>
+        <v>84</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>265</v>
@@ -5246,7 +5246,7 @@
         <v>33</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>373</v>
@@ -5278,7 +5278,7 @@
         <v>33</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>376</v>
@@ -5293,10 +5293,10 @@
         <v>77</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>378</v>
@@ -5310,7 +5310,7 @@
         <v>33</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>379</v>
@@ -5325,7 +5325,7 @@
         <v>77</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>290</v>
+        <v>113</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>275</v>
@@ -5357,13 +5357,13 @@
         <v>77</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>279</v>
+        <v>385</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -5456,31 +5456,31 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>110</v>
+        <v>84</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5488,31 +5488,31 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -5520,31 +5520,31 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>71</v>
+        <v>290</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -5552,31 +5552,31 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>71</v>
+        <v>222</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>85</v>
+        <v>150</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -5584,31 +5584,31 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>92</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>110</v>
+        <v>84</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>85</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -5616,22 +5616,22 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>98</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>401</v>
+        <v>51</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>401</v>
+        <v>51</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>402</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>71</v>
@@ -5648,10 +5648,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>404</v>
@@ -5666,7 +5666,7 @@
         <v>77</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>71</v>
+        <v>290</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>85</v>
@@ -5680,10 +5680,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>407</v>
@@ -5698,10 +5698,10 @@
         <v>77</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>110</v>
+        <v>290</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>85</v>
+        <v>136</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>409</v>
@@ -5712,10 +5712,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>410</v>
@@ -5730,10 +5730,10 @@
         <v>77</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>412</v>
@@ -5744,10 +5744,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>413</v>
@@ -5765,7 +5765,7 @@
         <v>71</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>415</v>
@@ -5776,10 +5776,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>416</v>
@@ -5794,10 +5794,10 @@
         <v>77</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>418</v>
@@ -5808,10 +5808,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>419</v>
@@ -5826,10 +5826,10 @@
         <v>77</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>421</v>
@@ -5840,10 +5840,10 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>422</v>
@@ -5861,7 +5861,7 @@
         <v>78</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>424</v>
@@ -5872,10 +5872,10 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>425</v>
@@ -5893,7 +5893,7 @@
         <v>71</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>427</v>
@@ -5904,10 +5904,10 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>428</v>
@@ -5922,10 +5922,10 @@
         <v>77</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>71</v>
+        <v>118</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>430</v>
@@ -5936,7 +5936,7 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>143</v>
@@ -5954,10 +5954,10 @@
         <v>77</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>433</v>
@@ -5968,10 +5968,10 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>434</v>
@@ -5986,10 +5986,10 @@
         <v>77</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>436</v>
@@ -6000,10 +6000,10 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>437</v>
@@ -6018,10 +6018,10 @@
         <v>77</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>439</v>
@@ -6032,10 +6032,10 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>440</v>
@@ -6050,10 +6050,10 @@
         <v>77</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>442</v>
@@ -6064,10 +6064,10 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>443</v>
@@ -6082,10 +6082,10 @@
         <v>77</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>252</v>
+        <v>141</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>445</v>
@@ -6096,10 +6096,10 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>446</v>
@@ -6114,10 +6114,10 @@
         <v>77</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>448</v>
@@ -6128,10 +6128,10 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>449</v>
@@ -6146,10 +6146,10 @@
         <v>77</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>451</v>
@@ -6160,10 +6160,10 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>452</v>
@@ -6178,10 +6178,10 @@
         <v>77</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>252</v>
+        <v>141</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>454</v>
@@ -6192,31 +6192,31 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>51</v>
+        <v>455</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>51</v>
+        <v>455</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>265</v>
+        <v>136</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -6224,31 +6224,31 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>265</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -6256,31 +6256,31 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>71</v>
+        <v>113</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>265</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -6288,31 +6288,31 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -6320,31 +6320,31 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>110</v>
+        <v>290</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -6352,28 +6352,28 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>471</v>
+        <v>282</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>472</v>
@@ -6617,7 +6617,7 @@
         <v>78</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>486</v>
@@ -6646,10 +6646,10 @@
         <v>77</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>84</v>
+        <v>222</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>489</v>
@@ -6663,7 +6663,7 @@
         <v>52</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>490</v>
@@ -6681,7 +6681,7 @@
         <v>290</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>492</v>
@@ -6695,7 +6695,7 @@
         <v>52</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>493</v>
@@ -6713,7 +6713,7 @@
         <v>71</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>495</v>
@@ -6727,7 +6727,7 @@
         <v>52</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>496</v>
@@ -6742,10 +6742,10 @@
         <v>77</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>498</v>
@@ -6759,7 +6759,7 @@
         <v>52</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>499</v>
@@ -6777,7 +6777,7 @@
         <v>71</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>501</v>
@@ -6791,7 +6791,7 @@
         <v>52</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>502</v>
@@ -6806,10 +6806,10 @@
         <v>77</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>504</v>
@@ -6823,7 +6823,7 @@
         <v>52</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>505</v>
@@ -6841,7 +6841,7 @@
         <v>71</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>507</v>
@@ -6855,7 +6855,7 @@
         <v>52</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>508</v>
@@ -6870,10 +6870,10 @@
         <v>77</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>510</v>
@@ -6887,7 +6887,7 @@
         <v>52</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>511</v>
@@ -6905,7 +6905,7 @@
         <v>71</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>513</v>
@@ -6919,7 +6919,7 @@
         <v>52</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>514</v>
@@ -6937,7 +6937,7 @@
         <v>71</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>516</v>
@@ -6983,7 +6983,7 @@
         <v>52</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>520</v>
@@ -7001,7 +7001,7 @@
         <v>71</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>522</v>
@@ -7015,7 +7015,7 @@
         <v>52</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>523</v>
@@ -7033,7 +7033,7 @@
         <v>290</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>525</v>
@@ -7047,7 +7047,7 @@
         <v>52</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>526</v>
@@ -7062,7 +7062,7 @@
         <v>77</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>275</v>
@@ -7079,7 +7079,7 @@
         <v>52</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>529</v>
@@ -7094,7 +7094,7 @@
         <v>77</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>84</v>
+        <v>222</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>265</v>
@@ -7111,7 +7111,7 @@
         <v>52</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>532</v>
@@ -7143,7 +7143,7 @@
         <v>52</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>535</v>
@@ -7158,10 +7158,10 @@
         <v>77</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>537</v>
@@ -7175,7 +7175,7 @@
         <v>52</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>538</v>
@@ -7190,7 +7190,7 @@
         <v>77</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>275</v>
@@ -7207,7 +7207,7 @@
         <v>52</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>541</v>
@@ -7239,7 +7239,7 @@
         <v>52</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>544</v>
@@ -7254,10 +7254,10 @@
         <v>77</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>546</v>
@@ -7271,7 +7271,7 @@
         <v>52</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>547</v>
@@ -7303,7 +7303,7 @@
         <v>52</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>550</v>
@@ -7335,7 +7335,7 @@
         <v>52</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>554</v>
@@ -7350,7 +7350,7 @@
         <v>77</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>556</v>

--- a/reports/빅딜/빅딜_mgf_matched_5_guilds.xlsx
+++ b/reports/빅딜/빅딜_mgf_matched_5_guilds.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1578" uniqueCount="558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1578" uniqueCount="561">
   <si>
     <t>guild_name</t>
   </si>
@@ -80,123 +80,129 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>376</t>
+    <t>377</t>
+  </si>
+  <si>
+    <t>14위</t>
+  </si>
+  <si>
+    <t>Lv.8</t>
+  </si>
+  <si>
+    <t>29명</t>
+  </si>
+  <si>
+    <t>127조 3213억 5790만</t>
+  </si>
+  <si>
+    <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
+  </si>
+  <si>
+    <t>망겜감별사</t>
+  </si>
+  <si>
+    <t>2026.04.11</t>
+  </si>
+  <si>
+    <t>피난민</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%ED%94%BC%EB%82%9C%EB%AF%BC</t>
+  </si>
+  <si>
+    <t>Scania 26</t>
+  </si>
+  <si>
+    <t>364</t>
+  </si>
+  <si>
+    <t>17위</t>
+  </si>
+  <si>
+    <t>137조 4077억 2612만</t>
+  </si>
+  <si>
+    <t>피난 오신 여러분 반갑습니다.</t>
+  </si>
+  <si>
+    <t>주방화</t>
+  </si>
+  <si>
+    <t>2026.04.10</t>
+  </si>
+  <si>
+    <t>부계둘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B6%80%EA%B3%84%EB%91%98</t>
+  </si>
+  <si>
+    <t>Scania 29</t>
+  </si>
+  <si>
+    <t>381</t>
+  </si>
+  <si>
+    <t>10위</t>
+  </si>
+  <si>
+    <t>Lv.6</t>
+  </si>
+  <si>
+    <t>124조 4701억 3596만</t>
+  </si>
+  <si>
+    <t>부계들 + 부계둘</t>
+  </si>
+  <si>
+    <t>홍춘삼</t>
+  </si>
+  <si>
+    <t>이고이스트</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%9D%B4%EA%B3%A0%EC%9D%B4%EC%8A%A4%ED%8A%B8</t>
+  </si>
+  <si>
+    <t>Scania 27</t>
+  </si>
+  <si>
+    <t>366</t>
+  </si>
+  <si>
+    <t>30위</t>
+  </si>
+  <si>
+    <t>Lv.7</t>
+  </si>
+  <si>
+    <t>30명</t>
+  </si>
+  <si>
+    <t>135조 5251억 2923만</t>
+  </si>
+  <si>
+    <t>가입문의 &amp;gt;&amp;gt; [ 에이비숍 , Eddy0825 ] &amp;lt;&amp;lt; 귓 1조 이상 :)</t>
+  </si>
+  <si>
+    <t>한도카드</t>
+  </si>
+  <si>
+    <t>밤과다람쥐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B0%A4%EA%B3%BC%EB%8B%A4%EB%9E%8C%EC%A5%90</t>
+  </si>
+  <si>
+    <t>Scania 5</t>
+  </si>
+  <si>
+    <t>326</t>
   </si>
   <si>
     <t>13위</t>
   </si>
   <si>
-    <t>Lv.8</t>
-  </si>
-  <si>
-    <t>29명</t>
-  </si>
-  <si>
-    <t>125조 5532억 9483만</t>
-  </si>
-  <si>
-    <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
-  </si>
-  <si>
-    <t>망겜감별사</t>
-  </si>
-  <si>
-    <t>2026.04.10</t>
-  </si>
-  <si>
-    <t>피난민</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%ED%94%BC%EB%82%9C%EB%AF%BC</t>
-  </si>
-  <si>
-    <t>Scania 26</t>
-  </si>
-  <si>
-    <t>362</t>
-  </si>
-  <si>
-    <t>17위</t>
-  </si>
-  <si>
-    <t>137조 4077억 2612만</t>
-  </si>
-  <si>
-    <t>피난 오신 여러분 반갑습니다.</t>
-  </si>
-  <si>
-    <t>주방화</t>
-  </si>
-  <si>
-    <t>부계둘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B6%80%EA%B3%84%EB%91%98</t>
-  </si>
-  <si>
-    <t>Scania 29</t>
-  </si>
-  <si>
-    <t>378</t>
-  </si>
-  <si>
-    <t>10위</t>
-  </si>
-  <si>
-    <t>Lv.6</t>
-  </si>
-  <si>
-    <t>124조 4701억 3596만</t>
-  </si>
-  <si>
-    <t>부계들 + 부계둘</t>
-  </si>
-  <si>
-    <t>홍춘삼</t>
-  </si>
-  <si>
-    <t>이고이스트</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%9D%B4%EA%B3%A0%EC%9D%B4%EC%8A%A4%ED%8A%B8</t>
-  </si>
-  <si>
-    <t>Scania 27</t>
-  </si>
-  <si>
-    <t>364</t>
-  </si>
-  <si>
-    <t>30위</t>
-  </si>
-  <si>
-    <t>Lv.7</t>
-  </si>
-  <si>
-    <t>30명</t>
-  </si>
-  <si>
-    <t>135조 5251억 2923만</t>
-  </si>
-  <si>
-    <t>가입문의 &amp;gt;&amp;gt; [ 에이비숍 , Eddy0825 ] &amp;lt;&amp;lt; 귓 1조 이상 :)</t>
-  </si>
-  <si>
-    <t>한도카드</t>
-  </si>
-  <si>
-    <t>밤과다람쥐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B0%A4%EA%B3%BC%EB%8B%A4%EB%9E%8C%EC%A5%90</t>
-  </si>
-  <si>
-    <t>Scania 5</t>
-  </si>
-  <si>
-    <t>324</t>
-  </si>
-  <si>
     <t>28명</t>
   </si>
   <si>
@@ -302,7 +308,7 @@
     <t>히어로</t>
   </si>
   <si>
-    <t>9조 2755억 5085만</t>
+    <t>9조 7846억 8335만</t>
   </si>
   <si>
     <t>5</t>
@@ -332,7 +338,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EC%B9%B4%EC%9A%B0</t>
   </si>
   <si>
-    <t>7조 2379억 2599만</t>
+    <t>7조 3832억 6175만</t>
   </si>
   <si>
     <t>7</t>
@@ -344,7 +350,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
   </si>
   <si>
-    <t>5조 9737억 2519만</t>
+    <t>5조 9851억 7276만</t>
   </si>
   <si>
     <t>8</t>
@@ -371,7 +377,7 @@
     <t>아크메이지(썬,콜)</t>
   </si>
   <si>
-    <t>4조 8908억 6341만</t>
+    <t>4조 9040억 3846만</t>
   </si>
   <si>
     <t>10</t>
@@ -401,7 +407,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
   </si>
   <si>
-    <t>3조 5074억 2328만</t>
+    <t>3조 7141억 4961만</t>
   </si>
   <si>
     <t>12</t>
@@ -425,7 +431,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%80%EA%B3%A0</t>
   </si>
   <si>
-    <t>3조 144억 7218만</t>
+    <t>3조 175억 79만</t>
   </si>
   <si>
     <t>14</t>
@@ -440,12 +446,24 @@
     <t>97</t>
   </si>
   <si>
-    <t>2조 5343억 6737만</t>
+    <t>2조 5711억 1705만</t>
   </si>
   <si>
     <t>15</t>
   </si>
   <si>
+    <t>강철고튠데</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EC%B2%A0%EA%B3%A0%ED%8A%A0%EB%8D%B0</t>
+  </si>
+  <si>
+    <t>2조 5595억 2만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
     <t>아르젠타</t>
   </si>
   <si>
@@ -455,19 +473,7 @@
     <t>96</t>
   </si>
   <si>
-    <t>2조 4792억 2203만</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>강철고튠데</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EC%B2%A0%EA%B3%A0%ED%8A%A0%EB%8D%B0</t>
-  </si>
-  <si>
-    <t>2조 4418억 6776만</t>
+    <t>2조 4827억 9180만</t>
   </si>
   <si>
     <t>17</t>
@@ -506,7 +512,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%AD%8C%ED%8C%8C%ED%8C%8C</t>
   </si>
   <si>
-    <t>2조 854억 1372만</t>
+    <t>2조 2120억 3922만</t>
   </si>
   <si>
     <t>20</t>
@@ -518,22 +524,34 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%95%EB%A5%B4%EC%BD%94%ED%94%84</t>
   </si>
   <si>
-    <t>2조 575억 7597만</t>
+    <t>2조 600억 2976만</t>
   </si>
   <si>
     <t>21</t>
   </si>
   <si>
+    <t>겨울바다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%A8%EC%9A%B8%EB%B0%94%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>2조 482억 8994만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
     <t>여븨</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%B8%A8</t>
   </si>
   <si>
-    <t>1조 9436억 1534만</t>
-  </si>
-  <si>
-    <t>22</t>
+    <t>1조 9464억 6561만</t>
+  </si>
+  <si>
+    <t>23</t>
   </si>
   <si>
     <t>제스프리</t>
@@ -545,18 +563,6 @@
     <t>1조 9311억 8518만</t>
   </si>
   <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>겨울바다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%A8%EC%9A%B8%EB%B0%94%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>1조 9074억 659만</t>
-  </si>
-  <si>
     <t>24</t>
   </si>
   <si>
@@ -572,6 +578,21 @@
     <t>25</t>
   </si>
   <si>
+    <t>불보독지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EB%B3%B4%EB%8F%85%EC%A7%80</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>1조 6526억 8209만</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
     <t>여눈</t>
   </si>
   <si>
@@ -581,21 +602,6 @@
     <t>1조 5909억 3493만</t>
   </si>
   <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>불보독지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EB%B3%B4%EB%8F%85%EC%A7%80</t>
-  </si>
-  <si>
-    <t>아크메이지(불,독)</t>
-  </si>
-  <si>
-    <t>1조 5603억 9115만</t>
-  </si>
-  <si>
     <t>27</t>
   </si>
   <si>
@@ -632,7 +638,7 @@
     <t>76</t>
   </si>
   <si>
-    <t>10억 3039만</t>
+    <t>10억 5189만</t>
   </si>
   <si>
     <t>샾한궁</t>
@@ -677,7 +683,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%83%9D%ED%96%88%EC%96%B4</t>
   </si>
   <si>
-    <t>9조 3382억 9591만</t>
+    <t>11조 6683억 8284만</t>
   </si>
   <si>
     <t>샾브샤브</t>
@@ -686,7 +692,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EB%B8%8C%EC%83%A4%EB%B8%8C</t>
   </si>
   <si>
-    <t>9조 1225억 1639만</t>
+    <t>9조 1410억 3665만</t>
   </si>
   <si>
     <t>샾밉당</t>
@@ -707,7 +713,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EA%BE%B8%EB%B6%95</t>
   </si>
   <si>
-    <t>5조 4511억 8191만</t>
+    <t>6조 47억 9517만</t>
   </si>
   <si>
     <t>쩡미니지후</t>
@@ -716,7 +722,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A9%A1%EB%AF%B8%EB%8B%88%EC%A7%80%ED%9B%84</t>
   </si>
   <si>
-    <t>3조 7991억 7310만</t>
+    <t>4조 236억 2723만</t>
   </si>
   <si>
     <t>소방담요</t>
@@ -725,7 +731,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EB%B0%A9%EB%8B%B4%EC%9A%94</t>
   </si>
   <si>
-    <t>3조 1039억 6544만</t>
+    <t>3조 1952억 2814만</t>
+  </si>
+  <si>
+    <t>샾프심</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%ED%94%84%EC%8B%AC</t>
+  </si>
+  <si>
+    <t>2조 3578억 7409만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EB%B0%A9%ED%99%94</t>
@@ -734,13 +749,13 @@
     <t>2조 3354억 9574만</t>
   </si>
   <si>
-    <t>샾프심</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%ED%94%84%EC%8B%AC</t>
-  </si>
-  <si>
-    <t>2조 3158억 6653만</t>
+    <t>샾오산</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%98%A4%EC%82%B0</t>
+  </si>
+  <si>
+    <t>2조 3073억 1285만</t>
   </si>
   <si>
     <t>상산의조자룡</t>
@@ -749,16 +764,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EC%82%B0%EC%9D%98%EC%A1%B0%EC%9E%90%EB%A3%A1</t>
   </si>
   <si>
-    <t>2조 2158억 7896만</t>
-  </si>
-  <si>
-    <t>샾오산</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%98%A4%EC%82%B0</t>
-  </si>
-  <si>
-    <t>2조 1574억 4420만</t>
+    <t>2조 2660억 2116만</t>
   </si>
   <si>
     <t>김퍽퍽</t>
@@ -767,7 +773,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%8D%BD%ED%8D%BD</t>
   </si>
   <si>
-    <t>1조 8756억 7377만</t>
+    <t>1조 9184억 8884만</t>
+  </si>
+  <si>
+    <t>샾오프</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%98%A4%ED%94%84</t>
+  </si>
+  <si>
+    <t>1조 6392억 4955만</t>
   </si>
   <si>
     <t>샾감자</t>
@@ -776,16 +791,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EA%B0%90%EC%9E%90</t>
   </si>
   <si>
-    <t>1조 5761억 4708만</t>
-  </si>
-  <si>
-    <t>샾오프</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%98%A4%ED%94%84</t>
-  </si>
-  <si>
-    <t>1조 5582억 599만</t>
+    <t>1조 6116억 2745만</t>
+  </si>
+  <si>
+    <t>oEMPo</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=oEMPo</t>
+  </si>
+  <si>
+    <t>1조 3672억 2971만</t>
   </si>
   <si>
     <t>무진미</t>
@@ -794,307 +809,307 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%A7%84%EB%AF%B8</t>
   </si>
   <si>
+    <t>1조 3439억 3411만</t>
+  </si>
+  <si>
+    <t>샾햇살</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%ED%96%87%EC%82%B4</t>
+  </si>
+  <si>
+    <t>1조 654억 1773만</t>
+  </si>
+  <si>
+    <t>이지아지콩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%A7%80%EC%95%84%EC%A7%80%EC%BD%A9</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>8868억 4949만</t>
+  </si>
+  <si>
+    <t>백수돼지로성</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%B1%EC%88%98%EB%8F%BC%EC%A7%80%EB%A1%9C%EC%84%B1</t>
+  </si>
+  <si>
+    <t>4881억 9538만</t>
+  </si>
+  <si>
+    <t>딱지냥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%94%B1%EC%A7%80%EB%83%A5</t>
+  </si>
+  <si>
+    <t>4337억 9550만</t>
+  </si>
+  <si>
+    <t>샾앤플랫</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%95%A4%ED%94%8C%EB%9E%AB</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>2316억 2601만</t>
+  </si>
+  <si>
+    <t>긩섷</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%A9%EC%84%B7</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>1864억 9941만</t>
+  </si>
+  <si>
+    <t>샾갈배</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EA%B0%88%EB%B0%B0</t>
+  </si>
+  <si>
+    <t>1673억 5338만</t>
+  </si>
+  <si>
+    <t>최훈석개멋져</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%ED%9B%88%EC%84%9D%EA%B0%9C%EB%A9%8B%EC%A0%B8</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>1450억 7248만</t>
+  </si>
+  <si>
+    <t>샾사니서리당</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%82%AC%EB%8B%88%EC%84%9C%EB%A6%AC%EB%8B%B9</t>
+  </si>
+  <si>
+    <t>비숍</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>1296억 8675만</t>
+  </si>
+  <si>
+    <t>커피둥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%ED%94%BC%EB%91%A5</t>
+  </si>
+  <si>
+    <t>1192억 3496만</t>
+  </si>
+  <si>
+    <t>둥둥콩이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%91%A5%EB%91%A5%EC%BD%A9%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>19조 3773억 6624만</t>
+  </si>
+  <si>
+    <t>가온스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%98%A8%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>17조 3732억 4655만</t>
+  </si>
+  <si>
+    <t>증권보이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A6%9D%EA%B6%8C%EB%B3%B4%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>12조 6269억 9088만</t>
+  </si>
+  <si>
+    <t>Canary</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Canary</t>
+  </si>
+  <si>
+    <t>12조 3252억 5686만</t>
+  </si>
+  <si>
+    <t>처히</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%98%ED%9E%88</t>
+  </si>
+  <si>
+    <t>9조 8029억 8581만</t>
+  </si>
+  <si>
+    <t>환생의불꼬츠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EC%83%9D%EC%9D%98%EB%B6%88%EA%BC%AC%EC%B8%A0</t>
+  </si>
+  <si>
+    <t>9조 4367억 6924만</t>
+  </si>
+  <si>
+    <t>밍진</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%8D%EC%A7%84</t>
+  </si>
+  <si>
+    <t>8조 9166억 6911만</t>
+  </si>
+  <si>
+    <t>Naco</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Naco</t>
+  </si>
+  <si>
+    <t>6조 8631억 7813만</t>
+  </si>
+  <si>
+    <t>AKPS</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=AKPS</t>
+  </si>
+  <si>
+    <t>5조 7025억 8245만</t>
+  </si>
+  <si>
+    <t>로베르트슈만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A1%9C%EB%B2%A0%EB%A5%B4%ED%8A%B8%EC%8A%88%EB%A7%8C</t>
+  </si>
+  <si>
+    <t>4조 6954억 1280만</t>
+  </si>
+  <si>
+    <t>사나이기백황</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%82%98%EC%9D%B4%EA%B8%B0%EB%B0%B1%ED%99%A9</t>
+  </si>
+  <si>
+    <t>3조 6567억 2052만</t>
+  </si>
+  <si>
+    <t>평평이형</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%89%ED%8F%89%EC%9D%B4%ED%98%95</t>
+  </si>
+  <si>
+    <t>2조 9795억 1723만</t>
+  </si>
+  <si>
+    <t>토미오카상</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%AF%B8%EC%98%A4%EC%B9%B4%EC%83%81</t>
+  </si>
+  <si>
+    <t>2조 8348억 2352만</t>
+  </si>
+  <si>
+    <t>천칠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%B9%A0</t>
+  </si>
+  <si>
+    <t>2조 6702억 2482만</t>
+  </si>
+  <si>
+    <t>토니워터</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%8B%88%EC%9B%8C%ED%84%B0</t>
+  </si>
+  <si>
+    <t>2조 6162억 1545만</t>
+  </si>
+  <si>
+    <t>화살대</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%82%B4%EB%8C%80</t>
+  </si>
+  <si>
+    <t>2조 3627억 7524만</t>
+  </si>
+  <si>
+    <t>런닝래빗</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9F%B0%EB%8B%9D%EB%9E%98%EB%B9%97</t>
+  </si>
+  <si>
+    <t>2조 198억 5360만</t>
+  </si>
+  <si>
+    <t>펑풀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8E%91%ED%92%80</t>
+  </si>
+  <si>
+    <t>1조 9607억 4471만</t>
+  </si>
+  <si>
+    <t>피어난</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%BC%EC%96%B4%EB%82%9C</t>
+  </si>
+  <si>
+    <t>1조 6873억 4877만</t>
+  </si>
+  <si>
+    <t>샤스찌에</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%A4%EC%8A%A4%EC%B0%8C%EC%97%90</t>
+  </si>
+  <si>
     <t>95</t>
   </si>
   <si>
-    <t>1조 3439억 3411만</t>
-  </si>
-  <si>
-    <t>oEMPo</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=oEMPo</t>
-  </si>
-  <si>
-    <t>1조 3336억 5678만</t>
-  </si>
-  <si>
-    <t>샾햇살</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%ED%96%87%EC%82%B4</t>
-  </si>
-  <si>
-    <t>1조 40억 8139만</t>
-  </si>
-  <si>
-    <t>이지아지콩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%A7%80%EC%95%84%EC%A7%80%EC%BD%A9</t>
-  </si>
-  <si>
-    <t>94</t>
-  </si>
-  <si>
-    <t>8868억 4949만</t>
-  </si>
-  <si>
-    <t>백수돼지로성</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%B1%EC%88%98%EB%8F%BC%EC%A7%80%EB%A1%9C%EC%84%B1</t>
-  </si>
-  <si>
-    <t>4745억 6122만</t>
-  </si>
-  <si>
-    <t>딱지냥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%94%B1%EC%A7%80%EB%83%A5</t>
-  </si>
-  <si>
-    <t>4109억 2332만</t>
-  </si>
-  <si>
-    <t>긩섷</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%A9%EC%84%B7</t>
-  </si>
-  <si>
-    <t>93</t>
-  </si>
-  <si>
-    <t>1864억 9941만</t>
-  </si>
-  <si>
-    <t>샾갈배</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EA%B0%88%EB%B0%B0</t>
-  </si>
-  <si>
-    <t>1673억 5338만</t>
-  </si>
-  <si>
-    <t>샾앤플랫</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%95%A4%ED%94%8C%EB%9E%AB</t>
-  </si>
-  <si>
-    <t>92</t>
-  </si>
-  <si>
-    <t>1582억 4444만</t>
-  </si>
-  <si>
-    <t>최훈석개멋져</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%ED%9B%88%EC%84%9D%EA%B0%9C%EB%A9%8B%EC%A0%B8</t>
-  </si>
-  <si>
-    <t>90</t>
-  </si>
-  <si>
-    <t>1450억 7248만</t>
-  </si>
-  <si>
-    <t>샾사니서리당</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%82%AC%EB%8B%88%EC%84%9C%EB%A6%AC%EB%8B%B9</t>
-  </si>
-  <si>
-    <t>비숍</t>
-  </si>
-  <si>
-    <t>91</t>
-  </si>
-  <si>
-    <t>1284억 6855만</t>
-  </si>
-  <si>
-    <t>커피둥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%ED%94%BC%EB%91%A5</t>
-  </si>
-  <si>
-    <t>1119억 5831만</t>
-  </si>
-  <si>
-    <t>가온스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%98%A8%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>17조 3732억 4655만</t>
-  </si>
-  <si>
-    <t>둥둥콩이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%91%A5%EB%91%A5%EC%BD%A9%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>16조 4186억 1612만</t>
-  </si>
-  <si>
-    <t>증권보이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A6%9D%EA%B6%8C%EB%B3%B4%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>12조 68억 2568만</t>
-  </si>
-  <si>
-    <t>Canary</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Canary</t>
-  </si>
-  <si>
-    <t>11조 5009억 9607만</t>
-  </si>
-  <si>
-    <t>처히</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%98%ED%9E%88</t>
-  </si>
-  <si>
-    <t>9조 7554억 7539만</t>
-  </si>
-  <si>
-    <t>환생의불꼬츠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EC%83%9D%EC%9D%98%EB%B6%88%EA%BC%AC%EC%B8%A0</t>
-  </si>
-  <si>
-    <t>9조 2454억 5199만</t>
-  </si>
-  <si>
-    <t>밍진</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%8D%EC%A7%84</t>
-  </si>
-  <si>
-    <t>8조 9166억 6911만</t>
-  </si>
-  <si>
-    <t>Naco</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Naco</t>
-  </si>
-  <si>
-    <t>6조 7523억 5853만</t>
-  </si>
-  <si>
-    <t>AKPS</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=AKPS</t>
-  </si>
-  <si>
-    <t>5조 644억 4933만</t>
-  </si>
-  <si>
-    <t>로베르트슈만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A1%9C%EB%B2%A0%EB%A5%B4%ED%8A%B8%EC%8A%88%EB%A7%8C</t>
-  </si>
-  <si>
-    <t>4조 6954억 1280만</t>
-  </si>
-  <si>
-    <t>사나이기백황</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%82%98%EC%9D%B4%EA%B8%B0%EB%B0%B1%ED%99%A9</t>
-  </si>
-  <si>
-    <t>3조 4297억 6701만</t>
-  </si>
-  <si>
-    <t>천칠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%B9%A0</t>
-  </si>
-  <si>
-    <t>2조 6702억 2482만</t>
-  </si>
-  <si>
-    <t>평평이형</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%89%ED%8F%89%EC%9D%B4%ED%98%95</t>
-  </si>
-  <si>
-    <t>2조 6657억 7512만</t>
-  </si>
-  <si>
-    <t>토니워터</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%8B%88%EC%9B%8C%ED%84%B0</t>
-  </si>
-  <si>
-    <t>2조 6162억 1545만</t>
-  </si>
-  <si>
-    <t>토미오카상</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%AF%B8%EC%98%A4%EC%B9%B4%EC%83%81</t>
-  </si>
-  <si>
-    <t>2조 5413억 4660만</t>
-  </si>
-  <si>
-    <t>화살대</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%82%B4%EB%8C%80</t>
-  </si>
-  <si>
-    <t>2조 1638억 2188만</t>
-  </si>
-  <si>
-    <t>런닝래빗</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9F%B0%EB%8B%9D%EB%9E%98%EB%B9%97</t>
-  </si>
-  <si>
-    <t>1조 9922억 3298만</t>
-  </si>
-  <si>
-    <t>펑풀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8E%91%ED%92%80</t>
-  </si>
-  <si>
-    <t>1조 9394억 7225만</t>
-  </si>
-  <si>
-    <t>피어난</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%BC%EC%96%B4%EB%82%9C</t>
-  </si>
-  <si>
-    <t>1조 6873억 4877만</t>
-  </si>
-  <si>
-    <t>샤스찌에</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%A4%EC%8A%A4%EC%B0%8C%EC%97%90</t>
-  </si>
-  <si>
-    <t>1조 1555억 4960만</t>
+    <t>1조 2240억 35만</t>
+  </si>
+  <si>
+    <t>보동핑</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%8F%99%ED%95%91</t>
+  </si>
+  <si>
+    <t>1조 1390억 7233만</t>
   </si>
   <si>
     <t>지니좋아요</t>
@@ -1103,16 +1118,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EB%8B%88%EC%A2%8B%EC%95%84%EC%9A%94</t>
   </si>
   <si>
-    <t>1조 348억 601만</t>
-  </si>
-  <si>
-    <t>보동핑</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%8F%99%ED%95%91</t>
-  </si>
-  <si>
-    <t>1조 167억 2526만</t>
+    <t>1조 666억 9786만</t>
   </si>
   <si>
     <t>싸토루</t>
@@ -1121,7 +1127,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%B8%ED%86%A0%EB%A3%A8</t>
   </si>
   <si>
-    <t>9713억 8758만</t>
+    <t>1조 477억 1901만</t>
   </si>
   <si>
     <t>2026년1월30일</t>
@@ -1130,13 +1136,13 @@
     <t>https://mgf.gg/contents/character.php?n=2026%EB%85%841%EC%9B%9430%EC%9D%BC</t>
   </si>
   <si>
-    <t>7424억 6962만</t>
+    <t>7942억 6933만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%99%8D%EC%B6%98%EC%82%BC</t>
   </si>
   <si>
-    <t>7170억 1216만</t>
+    <t>7940억 8278만</t>
   </si>
   <si>
     <t>찐곽정근</t>
@@ -1145,7 +1151,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B0%90%EA%B3%BD%EC%A0%95%EA%B7%BC</t>
   </si>
   <si>
-    <t>7074억 9433만</t>
+    <t>7912억 9292만</t>
   </si>
   <si>
     <t>Targa</t>
@@ -1163,7 +1169,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%A0%EB%91%98%EC%9D%B4%EC%97%90%EC%9A%94</t>
   </si>
   <si>
-    <t>5120억 6458만</t>
+    <t>5361억 4005만</t>
   </si>
   <si>
     <t>짱창훈</t>
@@ -1172,7 +1178,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%B1%EC%B0%BD%ED%9B%88</t>
   </si>
   <si>
-    <t>2730억 2959만</t>
+    <t>2736억 8603만</t>
   </si>
   <si>
     <t>30</t>
@@ -1187,7 +1193,7 @@
     <t>80</t>
   </si>
   <si>
-    <t>51억 9387만</t>
+    <t>52억 8190만</t>
   </si>
   <si>
     <t>마퀸</t>
@@ -1196,7 +1202,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%ED%80%B8</t>
   </si>
   <si>
-    <t>41조 8046억 1469만</t>
+    <t>44조 51억 7989만</t>
   </si>
   <si>
     <t>라면에계란탁</t>
@@ -1205,7 +1211,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EB%A9%B4%EC%97%90%EA%B3%84%EB%9E%80%ED%83%81</t>
   </si>
   <si>
-    <t>27조 944억 9823만</t>
+    <t>27조 5206억 3324만</t>
   </si>
   <si>
     <t>에이비숍</t>
@@ -1214,7 +1220,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EC%9D%B4%EB%B9%84%EC%88%8D</t>
   </si>
   <si>
-    <t>17조 4527억 529만</t>
+    <t>17조 4823억 394만</t>
   </si>
   <si>
     <t>환불카드</t>
@@ -1238,7 +1244,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%8F%84%EC%B9%B4%EB%93%9C</t>
   </si>
   <si>
-    <t>4조 5600억 4692만</t>
+    <t>4조 7320억 482만</t>
   </si>
   <si>
     <t>시글</t>
@@ -1265,7 +1271,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EA%B3%BC%EB%8B%B7</t>
   </si>
   <si>
-    <t>1조 9505억 2596만</t>
+    <t>2조 3266억 8637만</t>
+  </si>
+  <si>
+    <t>Eddy0825</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Eddy0825</t>
+  </si>
+  <si>
+    <t>1조 5159억 8227만</t>
   </si>
   <si>
     <t>토이감자</t>
@@ -1277,13 +1292,13 @@
     <t>1조 3297억 1328만</t>
   </si>
   <si>
-    <t>Eddy0825</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Eddy0825</t>
-  </si>
-  <si>
-    <t>1조 2699억 1720만</t>
+    <t>망치전문</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%98%EC%A0%84%EB%AC%B8</t>
+  </si>
+  <si>
+    <t>1조 2310억 3373만</t>
   </si>
   <si>
     <t>히히맘</t>
@@ -1292,16 +1307,25 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%ED%9E%88%EB%A7%98</t>
   </si>
   <si>
-    <t>1조 1570억 1834만</t>
-  </si>
-  <si>
-    <t>망치전문</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%98%EC%A0%84%EB%AC%B8</t>
-  </si>
-  <si>
-    <t>1조 946억 7036만</t>
+    <t>1조 2106억 9849만</t>
+  </si>
+  <si>
+    <t>돌격대원</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EA%B2%A9%EB%8C%80%EC%9B%90</t>
+  </si>
+  <si>
+    <t>1조 790억 9629만</t>
+  </si>
+  <si>
+    <t>닉커</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%89%EC%BB%A4</t>
+  </si>
+  <si>
+    <t>1조 468억 3525만</t>
   </si>
   <si>
     <t>핑와스</t>
@@ -1310,7 +1334,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%91%EC%99%80%EC%8A%A4</t>
   </si>
   <si>
-    <t>8953억 4884만</t>
+    <t>9138억 670만</t>
   </si>
   <si>
     <t>호츠</t>
@@ -1319,7 +1343,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%B8%A0</t>
   </si>
   <si>
-    <t>8817억 1133만</t>
+    <t>9109억 2570만</t>
+  </si>
+  <si>
+    <t>문뚱식</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%9A%B1%EC%8B%9D</t>
+  </si>
+  <si>
+    <t>9052억 4694만</t>
   </si>
   <si>
     <t>비숍덩구</t>
@@ -1328,34 +1361,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%88%8D%EB%8D%A9%EA%B5%AC</t>
   </si>
   <si>
-    <t>8325억 778만</t>
-  </si>
-  <si>
-    <t>닉커</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%89%EC%BB%A4</t>
-  </si>
-  <si>
-    <t>8229억 2581만</t>
-  </si>
-  <si>
-    <t>돌격대원</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EA%B2%A9%EB%8C%80%EC%9B%90</t>
-  </si>
-  <si>
-    <t>8183억 3301만</t>
-  </si>
-  <si>
-    <t>문뚱식</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%9A%B1%EC%8B%9D</t>
-  </si>
-  <si>
-    <t>8138억 1022만</t>
+    <t>9009억 1957만</t>
   </si>
   <si>
     <t>단풍a</t>
@@ -1364,7 +1370,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8Da</t>
   </si>
   <si>
-    <t>8039억 8999만</t>
+    <t>8257억 4459만</t>
+  </si>
+  <si>
+    <t>떼링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%96%BC%EB%A7%81</t>
+  </si>
+  <si>
+    <t>7458억 570만</t>
   </si>
   <si>
     <t>회원카드</t>
@@ -1373,16 +1388,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9A%8C%EC%9B%90%EC%B9%B4%EB%93%9C</t>
   </si>
   <si>
-    <t>7126억 7783만</t>
-  </si>
-  <si>
-    <t>떼링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%96%BC%EB%A7%81</t>
-  </si>
-  <si>
-    <t>7062억 4172만</t>
+    <t>7324억 3033만</t>
   </si>
   <si>
     <t>오보기다</t>
@@ -1403,22 +1409,22 @@
     <t>6583억 4222만</t>
   </si>
   <si>
+    <t>떵헤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%96%B5%ED%97%A4</t>
+  </si>
+  <si>
+    <t>6048억 1731만</t>
+  </si>
+  <si>
     <t>RIMS</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=RIMS</t>
   </si>
   <si>
-    <t>5821억 9350만</t>
-  </si>
-  <si>
-    <t>떵헤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%96%B5%ED%97%A4</t>
-  </si>
-  <si>
-    <t>5809억 6317만</t>
+    <t>5957억 2487만</t>
   </si>
   <si>
     <t>오말랑</t>
@@ -1427,7 +1433,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%A7%90%EB%9E%91</t>
   </si>
   <si>
-    <t>4763억 2057만</t>
+    <t>5071억 8373만</t>
   </si>
   <si>
     <t>직불카드</t>
@@ -1436,7 +1442,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%81%EB%B6%88%EC%B9%B4%EB%93%9C</t>
   </si>
   <si>
-    <t>2112억 3447만</t>
+    <t>2255억 948만</t>
   </si>
   <si>
     <t>채채자매</t>
@@ -1454,13 +1460,16 @@
     <t>https://mgf.gg/contents/character.php?n=MAKTO</t>
   </si>
   <si>
-    <t>87조 9937억 4731만</t>
+    <t>104</t>
+  </si>
+  <si>
+    <t>111조 2810억 2419만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EB%AF%B8%ED%98%95</t>
   </si>
   <si>
-    <t>50조 3315억 1281만</t>
+    <t>50조 4896억 2038만</t>
   </si>
   <si>
     <t>민헤</t>
@@ -1478,7 +1487,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EA%B3%84%EC%B1%94%ED%94%BC%EC%96%B8</t>
   </si>
   <si>
-    <t>9조 4057억 930만</t>
+    <t>10조 3718억 3648만</t>
   </si>
   <si>
     <t>I라헬I</t>
@@ -1487,7 +1496,7 @@
     <t>https://mgf.gg/contents/character.php?n=I%EB%9D%BC%ED%97%ACI</t>
   </si>
   <si>
-    <t>3조 695억 3442만</t>
+    <t>3조 1958억 8672만</t>
   </si>
   <si>
     <t>찐썽잉</t>
@@ -1496,7 +1505,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B0%90%EC%8D%BD%EC%9E%89</t>
   </si>
   <si>
-    <t>2조 1046억 8811만</t>
+    <t>2조 2203억 7898만</t>
   </si>
   <si>
     <t>건야웅</t>
@@ -1505,7 +1514,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B1%B4%EC%95%BC%EC%9B%85</t>
   </si>
   <si>
-    <t>1조 9254억 7512만</t>
+    <t>2조 393억 8672만</t>
   </si>
   <si>
     <t>보꿍</t>
@@ -1532,7 +1541,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B9%98%ED%82%A8v</t>
   </si>
   <si>
-    <t>1조 1922억 5473만</t>
+    <t>1조 2546억 5507만</t>
   </si>
   <si>
     <t>레제내꺼야</t>
@@ -1541,7 +1550,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A0%88%EC%A0%9C%EB%82%B4%EA%BA%BC%EC%95%BC</t>
   </si>
   <si>
-    <t>8961억 5267만</t>
+    <t>9440억 8488만</t>
   </si>
   <si>
     <t>키죠</t>
@@ -1550,7 +1559,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%EC%A3%A0</t>
   </si>
   <si>
-    <t>8316억 8048만</t>
+    <t>8460억 3852만</t>
+  </si>
+  <si>
+    <t>묨밍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%A8%EB%B0%8D</t>
+  </si>
+  <si>
+    <t>8330억 9581만</t>
   </si>
   <si>
     <t>S2지존</t>
@@ -1559,16 +1577,7 @@
     <t>https://mgf.gg/contents/character.php?n=S2%EC%A7%80%EC%A1%B4</t>
   </si>
   <si>
-    <t>7959억 2122만</t>
-  </si>
-  <si>
-    <t>묨밍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%A8%EB%B0%8D</t>
-  </si>
-  <si>
-    <t>7618억 2362만</t>
+    <t>8047억 7661만</t>
   </si>
   <si>
     <t>하얀물개</t>
@@ -1577,7 +1586,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%96%80%EB%AC%BC%EA%B0%9C</t>
   </si>
   <si>
-    <t>6229억 7916만</t>
+    <t>7486억 9717만</t>
   </si>
   <si>
     <t>초코냥부하</t>
@@ -1586,7 +1595,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%BD%94%EB%83%A5%EB%B6%80%ED%95%98</t>
   </si>
   <si>
-    <t>5556억 6668만</t>
+    <t>5783억 1003만</t>
   </si>
   <si>
     <t>장빵구</t>
@@ -1595,7 +1604,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EB%B9%B5%EA%B5%AC</t>
   </si>
   <si>
-    <t>5419억 8997만</t>
+    <t>5600억 447만</t>
+  </si>
+  <si>
+    <t>환불냠냠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EB%B6%88%EB%83%A0%EB%83%A0</t>
+  </si>
+  <si>
+    <t>4690억 2113만</t>
   </si>
   <si>
     <t>레피스나2</t>
@@ -1604,16 +1622,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A0%88%ED%94%BC%EC%8A%A4%EB%82%982</t>
   </si>
   <si>
-    <t>4598억 6348만</t>
-  </si>
-  <si>
-    <t>환불냠냠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EB%B6%88%EB%83%A0%EB%83%A0</t>
-  </si>
-  <si>
-    <t>4596억 3206만</t>
+    <t>4656억 7903만</t>
   </si>
   <si>
     <t>혼자가최고</t>
@@ -1631,7 +1640,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%9D%EC%9A%A9%EC%9E%89</t>
   </si>
   <si>
-    <t>3936억 3889만</t>
+    <t>4268억 6235만</t>
   </si>
   <si>
     <t>망복복</t>
@@ -1640,7 +1649,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EB%B3%B5%EB%B3%B5</t>
   </si>
   <si>
-    <t>3742억 3818만</t>
+    <t>3846억 1366만</t>
   </si>
   <si>
     <t>모몬쌍</t>
@@ -1649,7 +1658,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EB%AA%AC%EC%8C%8D</t>
   </si>
   <si>
-    <t>2440억 7917만</t>
+    <t>2461억 6727만</t>
   </si>
   <si>
     <t>우주강아지</t>
@@ -1688,7 +1697,7 @@
     <t>86</t>
   </si>
   <si>
-    <t>681억 6134만</t>
+    <t>726억 6028만</t>
   </si>
   <si>
     <t>만년설딸기</t>
@@ -1700,7 +1709,7 @@
     <t>84</t>
   </si>
   <si>
-    <t>193억 122만</t>
+    <t>225억 116만</t>
   </si>
 </sst>
 </file>
@@ -2199,130 +2208,130 @@
         <v>32</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>20</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -2358,28 +2367,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -2390,7 +2399,7 @@
         <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>23</v>
@@ -2399,19 +2408,19 @@
         <v>23</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -2422,28 +2431,28 @@
         <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -2454,28 +2463,28 @@
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -2486,28 +2495,28 @@
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="I5" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -2518,28 +2527,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -2550,28 +2559,28 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -2582,28 +2591,28 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -2614,28 +2623,28 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -2646,28 +2655,28 @@
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -2678,28 +2687,28 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -2710,28 +2719,28 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -2742,28 +2751,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -2774,28 +2783,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -2806,28 +2815,28 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -2838,28 +2847,28 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -2870,28 +2879,28 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>119</v>
+        <v>147</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -2902,28 +2911,28 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -2934,28 +2943,28 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -2966,28 +2975,28 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -2998,28 +3007,28 @@
         <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3030,28 +3039,28 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>71</v>
+        <v>115</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>85</v>
+        <v>152</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3062,28 +3071,28 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>136</v>
+        <v>87</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3094,28 +3103,28 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3126,28 +3135,28 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3158,28 +3167,28 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>71</v>
+        <v>185</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -3190,28 +3199,28 @@
         <v>13</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>187</v>
+        <v>73</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3222,28 +3231,28 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3254,28 +3263,28 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -3286,28 +3295,28 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -3370,28 +3379,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -3402,31 +3411,31 @@
         <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3434,31 +3443,31 @@
         <v>25</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3466,31 +3475,31 @@
         <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -3498,31 +3507,31 @@
         <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3530,31 +3539,31 @@
         <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3562,31 +3571,31 @@
         <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -3594,31 +3603,31 @@
         <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -3626,31 +3635,31 @@
         <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -3658,31 +3667,31 @@
         <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -3690,31 +3699,31 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -3722,31 +3731,31 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>32</v>
+        <v>235</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>32</v>
+        <v>235</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -3754,31 +3763,31 @@
         <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>235</v>
+        <v>32</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>235</v>
+        <v>32</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -3786,31 +3795,31 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -3818,31 +3827,31 @@
         <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>150</v>
+        <v>121</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -3850,31 +3859,31 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -3882,31 +3891,31 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -3914,31 +3923,31 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -3946,31 +3955,31 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>71</v>
+        <v>115</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>255</v>
+        <v>147</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -3978,31 +3987,31 @@
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>113</v>
+        <v>73</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -4010,31 +4019,31 @@
         <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -4042,31 +4051,31 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -4074,31 +4083,31 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -4106,31 +4115,31 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -4138,31 +4147,31 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -4170,31 +4179,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>113</v>
+        <v>73</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -4202,31 +4211,31 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H27" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>282</v>
-      </c>
       <c r="I27" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -4234,31 +4243,31 @@
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -4266,31 +4275,31 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -4298,31 +4307,31 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -4382,28 +4391,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -4411,962 +4420,962 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>119</v>
-      </c>
       <c r="I12" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>222</v>
+        <v>73</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>119</v>
+        <v>147</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>71</v>
+        <v>224</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>136</v>
-      </c>
       <c r="I16" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H18" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>141</v>
-      </c>
       <c r="I18" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>255</v>
+        <v>356</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>255</v>
+        <v>356</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -5427,28 +5436,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -5456,930 +5465,930 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>79</v>
-      </c>
       <c r="I4" s="2" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>118</v>
+        <v>73</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>113</v>
+        <v>73</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H18" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>141</v>
-      </c>
       <c r="I18" s="2" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>71</v>
+        <v>115</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>265</v>
+        <v>356</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>71</v>
+        <v>115</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>113</v>
+        <v>73</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>265</v>
+        <v>356</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -6430,7 +6439,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="17.7109375" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6439,28 +6448,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -6468,898 +6477,898 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>72</v>
+        <v>477</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="I3" s="2" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>150</v>
+        <v>121</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>255</v>
+        <v>147</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>255</v>
+        <v>147</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>141</v>
+        <v>356</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>265</v>
+        <v>356</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>290</v>
+        <v>86</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>84</v>
+        <v>291</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>275</v>
+        <v>356</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/reports/빅딜/빅딜_mgf_matched_5_guilds.xlsx
+++ b/reports/빅딜/빅딜_mgf_matched_5_guilds.xlsx
@@ -9,18 +9,18 @@
   <sheets>
     <sheet name="guilds" sheetId="1" r:id="rId1"/>
     <sheet name="빅딜" sheetId="2" r:id="rId2"/>
-    <sheet name="피난민" sheetId="3" r:id="rId3"/>
-    <sheet name="부계둘" sheetId="4" r:id="rId4"/>
+    <sheet name="부계둘" sheetId="3" r:id="rId3"/>
+    <sheet name="피난민" sheetId="4" r:id="rId4"/>
     <sheet name="이고이스트" sheetId="5" r:id="rId5"/>
     <sheet name="밤과다람쥐" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">밤과다람쥐!$A$1:$J$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">부계둘!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">부계둘!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">이고이스트!$A$1:$J$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">피난민!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">이고이스트!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">피난민!$A$1:$J$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -104,6 +104,36 @@
     <t>2026.04.11</t>
   </si>
   <si>
+    <t>부계둘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B6%80%EA%B3%84%EB%91%98</t>
+  </si>
+  <si>
+    <t>Scania 29</t>
+  </si>
+  <si>
+    <t>381</t>
+  </si>
+  <si>
+    <t>10위</t>
+  </si>
+  <si>
+    <t>Lv.6</t>
+  </si>
+  <si>
+    <t>124조 4701억 3596만</t>
+  </si>
+  <si>
+    <t>부계들 + 부계둘</t>
+  </si>
+  <si>
+    <t>홍춘삼</t>
+  </si>
+  <si>
+    <t>2026.04.10</t>
+  </si>
+  <si>
     <t>피난민</t>
   </si>
   <si>
@@ -128,36 +158,6 @@
     <t>주방화</t>
   </si>
   <si>
-    <t>2026.04.10</t>
-  </si>
-  <si>
-    <t>부계둘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B6%80%EA%B3%84%EB%91%98</t>
-  </si>
-  <si>
-    <t>Scania 29</t>
-  </si>
-  <si>
-    <t>381</t>
-  </si>
-  <si>
-    <t>10위</t>
-  </si>
-  <si>
-    <t>Lv.6</t>
-  </si>
-  <si>
-    <t>124조 4701억 3596만</t>
-  </si>
-  <si>
-    <t>부계들 + 부계둘</t>
-  </si>
-  <si>
-    <t>홍춘삼</t>
-  </si>
-  <si>
     <t>이고이스트</t>
   </si>
   <si>
@@ -254,7 +254,7 @@
     <t>103</t>
   </si>
   <si>
-    <t>15조 258억 4050만</t>
+    <t>15조 1221억 9952만</t>
   </si>
   <si>
     <t>2</t>
@@ -308,7 +308,7 @@
     <t>히어로</t>
   </si>
   <si>
-    <t>9조 7846억 8335만</t>
+    <t>10조 6714억 9011만</t>
   </si>
   <si>
     <t>5</t>
@@ -323,39 +323,54 @@
     <t>보우마스터</t>
   </si>
   <si>
+    <t>9조 4831억 8007만</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>단풍카우</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EC%B9%B4%EC%9A%B0</t>
+  </si>
+  <si>
+    <t>7조 3899억 9567만</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>아르미느</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
+  </si>
+  <si>
     <t>101</t>
   </si>
   <si>
-    <t>8조 7601억 85만</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>단풍카우</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EC%B9%B4%EC%9A%B0</t>
-  </si>
-  <si>
-    <t>7조 3832억 6175만</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>아르미느</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
-  </si>
-  <si>
-    <t>5조 9851억 7276만</t>
+    <t>6조 468억 64만</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
+    <t>굴러가는일상</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%B4%EB%9F%AC%EA%B0%80%EB%8A%94%EC%9D%BC%EC%83%81</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
+    <t>5조 1968억 8766만</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
     <t>포스코퓨처엠</t>
   </si>
   <si>
@@ -365,21 +380,6 @@
     <t>5조 1472억 5810만</t>
   </si>
   <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>굴러가는일상</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%B4%EB%9F%AC%EA%B0%80%EB%8A%94%EC%9D%BC%EC%83%81</t>
-  </si>
-  <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
-    <t>4조 9040억 3846만</t>
-  </si>
-  <si>
     <t>10</t>
   </si>
   <si>
@@ -407,7 +407,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
   </si>
   <si>
-    <t>3조 7141억 4961만</t>
+    <t>3조 8750억 1931만</t>
   </si>
   <si>
     <t>12</t>
@@ -437,19 +437,43 @@
     <t>14</t>
   </si>
   <si>
+    <t>쭌파파</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%AD%8C%ED%8C%8C%ED%8C%8C</t>
+  </si>
+  <si>
+    <t>2조 6747억 6521만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>아르젠타</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EC%A0%A0%ED%83%80</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>2조 5940억 8239만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
     <t>비스밤</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
   </si>
   <si>
-    <t>97</t>
-  </si>
-  <si>
     <t>2조 5711억 1705만</t>
   </si>
   <si>
-    <t>15</t>
+    <t>17</t>
   </si>
   <si>
     <t>강철고튠데</t>
@@ -461,168 +485,144 @@
     <t>2조 5595억 2만</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>아르젠타</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EC%A0%A0%ED%83%80</t>
+    <t>18</t>
+  </si>
+  <si>
+    <t>꾸르꾸르</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A5%B4%EA%BE%B8%EB%A5%B4</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>2조 3765억 8123만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>민들레꽃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
+  </si>
+  <si>
+    <t>2조 3302억 2720만</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>덕르코프</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8D%95%EB%A5%B4%EC%BD%94%ED%94%84</t>
+  </si>
+  <si>
+    <t>2조 2480억 2119만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>겨울바다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%A8%EC%9A%B8%EB%B0%94%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>2조 1038억 6635만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>여븨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%B8%A8</t>
+  </si>
+  <si>
+    <t>2조 737억 3833만</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>제스프리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EC%8A%A4%ED%94%84%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>1조 9311억 8518만</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>불보독지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EB%B3%B4%EB%8F%85%EC%A7%80</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>1조 9171억 4797만</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>여눈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%88%88</t>
+  </si>
+  <si>
+    <t>1조 7856억 5439만</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>플로우00</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%8C%EB%A1%9C%EC%9A%B000</t>
+  </si>
+  <si>
+    <t>1조 6923억 5834만</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>데드캣</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8D%B0%EB%93%9C%EC%BA%A3</t>
+  </si>
+  <si>
+    <t>1조 6435억 7464만</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>욤지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A4%EC%A7%80</t>
   </si>
   <si>
     <t>96</t>
   </si>
   <si>
-    <t>2조 4827억 9180만</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>꾸르꾸르</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A5%B4%EA%BE%B8%EB%A5%B4</t>
-  </si>
-  <si>
-    <t>98</t>
-  </si>
-  <si>
-    <t>2조 3765억 8123만</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>민들레꽃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
-  </si>
-  <si>
-    <t>2조 3302억 2720만</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>쭌파파</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%AD%8C%ED%8C%8C%ED%8C%8C</t>
-  </si>
-  <si>
-    <t>2조 2120억 3922만</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>덕르코프</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8D%95%EB%A5%B4%EC%BD%94%ED%94%84</t>
-  </si>
-  <si>
-    <t>2조 600억 2976만</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>겨울바다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%A8%EC%9A%B8%EB%B0%94%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>2조 482억 8994만</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>여븨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%B8%A8</t>
-  </si>
-  <si>
-    <t>1조 9464억 6561만</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>제스프리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EC%8A%A4%ED%94%84%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>1조 9311억 8518만</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>플로우00</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%8C%EB%A1%9C%EC%9A%B000</t>
-  </si>
-  <si>
-    <t>1조 6923억 5834만</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>불보독지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EB%B3%B4%EB%8F%85%EC%A7%80</t>
-  </si>
-  <si>
-    <t>아크메이지(불,독)</t>
-  </si>
-  <si>
-    <t>1조 6526억 8209만</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>여눈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%88%88</t>
-  </si>
-  <si>
-    <t>1조 5909억 3493만</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>데드캣</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8D%B0%EB%93%9C%EC%BA%A3</t>
-  </si>
-  <si>
-    <t>1조 5363억 9751만</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>욤지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A4%EC%A7%80</t>
-  </si>
-  <si>
     <t>1조 2381억 1362만</t>
   </si>
   <si>
@@ -638,7 +638,289 @@
     <t>76</t>
   </si>
   <si>
-    <t>10억 5189만</t>
+    <t>11억 9359만</t>
+  </si>
+  <si>
+    <t>증권보이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A6%9D%EA%B6%8C%EB%B3%B4%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>20조 4898억 61만</t>
+  </si>
+  <si>
+    <t>둥둥콩이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%91%A5%EB%91%A5%EC%BD%A9%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>19조 9942억 330만</t>
+  </si>
+  <si>
+    <t>가온스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%98%A8%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>17조 4585억 7977만</t>
+  </si>
+  <si>
+    <t>Canary</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Canary</t>
+  </si>
+  <si>
+    <t>15조 8193억 825만</t>
+  </si>
+  <si>
+    <t>처히</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%98%ED%9E%88</t>
+  </si>
+  <si>
+    <t>11조 4373억 7655만</t>
+  </si>
+  <si>
+    <t>환생의불꼬츠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EC%83%9D%EC%9D%98%EB%B6%88%EA%BC%AC%EC%B8%A0</t>
+  </si>
+  <si>
+    <t>10조 9549억 8302만</t>
+  </si>
+  <si>
+    <t>밍진</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%8D%EC%A7%84</t>
+  </si>
+  <si>
+    <t>8조 9166억 6911만</t>
+  </si>
+  <si>
+    <t>Naco</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Naco</t>
+  </si>
+  <si>
+    <t>6조 9849억 7135만</t>
+  </si>
+  <si>
+    <t>AKPS</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=AKPS</t>
+  </si>
+  <si>
+    <t>6조 5629억 7412만</t>
+  </si>
+  <si>
+    <t>사나이기백황</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%82%98%EC%9D%B4%EA%B8%B0%EB%B0%B1%ED%99%A9</t>
+  </si>
+  <si>
+    <t>3조 7356억 3356만</t>
+  </si>
+  <si>
+    <t>토미오카상</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%AF%B8%EC%98%A4%EC%B9%B4%EC%83%81</t>
+  </si>
+  <si>
+    <t>3조 3002억 4541만</t>
+  </si>
+  <si>
+    <t>평평이형</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%89%ED%8F%89%EC%9D%B4%ED%98%95</t>
+  </si>
+  <si>
+    <t>3조 906억 3513만</t>
+  </si>
+  <si>
+    <t>천칠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%B9%A0</t>
+  </si>
+  <si>
+    <t>팔라딘</t>
+  </si>
+  <si>
+    <t>2조 6702억 2482만</t>
+  </si>
+  <si>
+    <t>토니워터</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%8B%88%EC%9B%8C%ED%84%B0</t>
+  </si>
+  <si>
+    <t>2조 6162억 1545만</t>
+  </si>
+  <si>
+    <t>화살대</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%82%B4%EB%8C%80</t>
+  </si>
+  <si>
+    <t>2조 4258억 6186만</t>
+  </si>
+  <si>
+    <t>펑풀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8E%91%ED%92%80</t>
+  </si>
+  <si>
+    <t>2조 4059억 6852만</t>
+  </si>
+  <si>
+    <t>런닝래빗</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9F%B0%EB%8B%9D%EB%9E%98%EB%B9%97</t>
+  </si>
+  <si>
+    <t>2조 3545억 5014만</t>
+  </si>
+  <si>
+    <t>피어난</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%BC%EC%96%B4%EB%82%9C</t>
+  </si>
+  <si>
+    <t>2조 305억 8537만</t>
+  </si>
+  <si>
+    <t>샤스찌에</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%A4%EC%8A%A4%EC%B0%8C%EC%97%90</t>
+  </si>
+  <si>
+    <t>1조 4976억 9640만</t>
+  </si>
+  <si>
+    <t>보동핑</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%8F%99%ED%95%91</t>
+  </si>
+  <si>
+    <t>1조 1534억 4683만</t>
+  </si>
+  <si>
+    <t>싸토루</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B8%ED%86%A0%EB%A3%A8</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>1조 1480억 9108만</t>
+  </si>
+  <si>
+    <t>지니좋아요</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EB%8B%88%EC%A2%8B%EC%95%84%EC%9A%94</t>
+  </si>
+  <si>
+    <t>1조 666억 9786만</t>
+  </si>
+  <si>
+    <t>2026년1월30일</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=2026%EB%85%841%EC%9B%9430%EC%9D%BC</t>
+  </si>
+  <si>
+    <t>1조 129억 4198만</t>
+  </si>
+  <si>
+    <t>찐곽정근</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B0%90%EA%B3%BD%EC%A0%95%EA%B7%BC</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>1조 24억 1640만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%8D%EC%B6%98%EC%82%BC</t>
+  </si>
+  <si>
+    <t>8747억 2403만</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Targa</t>
+  </si>
+  <si>
+    <t>5665억 5826만</t>
+  </si>
+  <si>
+    <t>애둘이에요</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%A0%EB%91%98%EC%9D%B4%EC%97%90%EC%9A%94</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>5424억 3794만</t>
+  </si>
+  <si>
+    <t>짱창훈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%B1%EC%B0%BD%ED%9B%88</t>
+  </si>
+  <si>
+    <t>3382억 604만</t>
+  </si>
+  <si>
+    <t>구리구리뽕리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%A6%AC%EA%B5%AC%EB%A6%AC%EB%BD%95%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>52억 8190만</t>
+  </si>
+  <si>
+    <t>샾온</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%98%A8</t>
+  </si>
+  <si>
+    <t>35조 551억 5969만</t>
   </si>
   <si>
     <t>샾한궁</t>
@@ -647,16 +929,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%ED%95%9C%EA%B6%81</t>
   </si>
   <si>
-    <t>27조 6316억 6311만</t>
-  </si>
-  <si>
-    <t>샾온</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%98%A8</t>
-  </si>
-  <si>
-    <t>20조 4459억 2037만</t>
+    <t>28조 740억 9066만</t>
   </si>
   <si>
     <t>샾살개</t>
@@ -692,7 +965,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EB%B8%8C%EC%83%A4%EB%B8%8C</t>
   </si>
   <si>
-    <t>9조 1410억 3665만</t>
+    <t>9조 4038억 7114만</t>
   </si>
   <si>
     <t>샾밉당</t>
@@ -701,10 +974,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EB%B0%89%EB%8B%B9</t>
   </si>
   <si>
-    <t>팔라딘</t>
-  </si>
-  <si>
-    <t>8조 1605억 5099만</t>
+    <t>8조 5617억 8638만</t>
   </si>
   <si>
     <t>샾꾸붕</t>
@@ -713,7 +983,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EA%BE%B8%EB%B6%95</t>
   </si>
   <si>
-    <t>6조 47억 9517만</t>
+    <t>6조 355억 4707만</t>
   </si>
   <si>
     <t>쩡미니지후</t>
@@ -722,7 +992,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A9%A1%EB%AF%B8%EB%8B%88%EC%A7%80%ED%9B%84</t>
   </si>
   <si>
-    <t>4조 236억 2723만</t>
+    <t>4조 2574억 6994만</t>
   </si>
   <si>
     <t>소방담요</t>
@@ -734,13 +1004,22 @@
     <t>3조 1952억 2814만</t>
   </si>
   <si>
+    <t>상산의조자룡</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EC%82%B0%EC%9D%98%EC%A1%B0%EC%9E%90%EB%A3%A1</t>
+  </si>
+  <si>
+    <t>3조 1638억 2823만</t>
+  </si>
+  <si>
     <t>샾프심</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%ED%94%84%EC%8B%AC</t>
   </si>
   <si>
-    <t>2조 3578억 7409만</t>
+    <t>2조 6800억 1132만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EB%B0%A9%ED%99%94</t>
@@ -755,16 +1034,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%98%A4%EC%82%B0</t>
   </si>
   <si>
-    <t>2조 3073억 1285만</t>
-  </si>
-  <si>
-    <t>상산의조자룡</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EC%82%B0%EC%9D%98%EC%A1%B0%EC%9E%90%EB%A3%A1</t>
-  </si>
-  <si>
-    <t>2조 2660억 2116만</t>
+    <t>2조 3342억 6132만</t>
   </si>
   <si>
     <t>김퍽퍽</t>
@@ -773,7 +1043,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%8D%BD%ED%8D%BD</t>
   </si>
   <si>
-    <t>1조 9184억 8884만</t>
+    <t>2조 1388억 1231만</t>
   </si>
   <si>
     <t>샾오프</t>
@@ -782,7 +1052,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%98%A4%ED%94%84</t>
   </si>
   <si>
-    <t>1조 6392억 4955만</t>
+    <t>1조 6634억 6181만</t>
   </si>
   <si>
     <t>샾감자</t>
@@ -794,22 +1064,22 @@
     <t>1조 6116억 2745만</t>
   </si>
   <si>
+    <t>무진미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%A7%84%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>1조 5577억 7193만</t>
+  </si>
+  <si>
     <t>oEMPo</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=oEMPo</t>
   </si>
   <si>
-    <t>1조 3672억 2971만</t>
-  </si>
-  <si>
-    <t>무진미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%A7%84%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>1조 3439억 3411만</t>
+    <t>1조 3704억 7106만</t>
   </si>
   <si>
     <t>샾햇살</t>
@@ -818,7 +1088,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%ED%96%87%EC%82%B4</t>
   </si>
   <si>
-    <t>1조 654억 1773만</t>
+    <t>1조 833억 4380만</t>
   </si>
   <si>
     <t>이지아지콩</t>
@@ -827,10 +1097,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%A7%80%EC%95%84%EC%A7%80%EC%BD%A9</t>
   </si>
   <si>
-    <t>94</t>
-  </si>
-  <si>
-    <t>8868억 4949만</t>
+    <t>9566억 7217만</t>
   </si>
   <si>
     <t>백수돼지로성</t>
@@ -839,7 +1106,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%B1%EC%88%98%EB%8F%BC%EC%A7%80%EB%A1%9C%EC%84%B1</t>
   </si>
   <si>
-    <t>4881억 9538만</t>
+    <t>5265억 7331만</t>
   </si>
   <si>
     <t>딱지냥</t>
@@ -848,7 +1115,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%94%B1%EC%A7%80%EB%83%A5</t>
   </si>
   <si>
-    <t>4337억 9550만</t>
+    <t>4512억 5148만</t>
   </si>
   <si>
     <t>샾앤플랫</t>
@@ -857,826 +1124,571 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%95%A4%ED%94%8C%EB%9E%AB</t>
   </si>
   <si>
+    <t>2316억 2601만</t>
+  </si>
+  <si>
+    <t>긩섷</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%A9%EC%84%B7</t>
+  </si>
+  <si>
+    <t>1864억 9941만</t>
+  </si>
+  <si>
+    <t>샾갈배</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EA%B0%88%EB%B0%B0</t>
+  </si>
+  <si>
+    <t>1862억 1727만</t>
+  </si>
+  <si>
+    <t>최훈석개멋져</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%ED%9B%88%EC%84%9D%EA%B0%9C%EB%A9%8B%EC%A0%B8</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>1515억 6732만</t>
+  </si>
+  <si>
+    <t>샾사니서리당</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%82%AC%EB%8B%88%EC%84%9C%EB%A6%AC%EB%8B%B9</t>
+  </si>
+  <si>
+    <t>비숍</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>1346억 4398만</t>
+  </si>
+  <si>
+    <t>커피둥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%ED%94%BC%EB%91%A5</t>
+  </si>
+  <si>
+    <t>1200억 9858만</t>
+  </si>
+  <si>
+    <t>마퀸</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%ED%80%B8</t>
+  </si>
+  <si>
+    <t>44조 6786억 4350만</t>
+  </si>
+  <si>
+    <t>라면에계란탁</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EB%A9%B4%EC%97%90%EA%B3%84%EB%9E%80%ED%83%81</t>
+  </si>
+  <si>
+    <t>29조 7729억 2533만</t>
+  </si>
+  <si>
+    <t>에이비숍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EC%9D%B4%EB%B9%84%EC%88%8D</t>
+  </si>
+  <si>
+    <t>18조 8542억 5406만</t>
+  </si>
+  <si>
+    <t>환불카드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EB%B6%88%EC%B9%B4%EB%93%9C</t>
+  </si>
+  <si>
+    <t>10조 6115억 767만</t>
+  </si>
+  <si>
+    <t>아빠카드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%B9%A0%EC%B9%B4%EB%93%9C</t>
+  </si>
+  <si>
+    <t>7조 2480억 6688만</t>
+  </si>
+  <si>
+    <t>시글</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EA%B8%80</t>
+  </si>
+  <si>
+    <t>6조 5681억 7800만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%8F%84%EC%B9%B4%EB%93%9C</t>
+  </si>
+  <si>
+    <t>4조 9365억 4349만</t>
+  </si>
+  <si>
+    <t>공사과장</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EC%82%AC%EA%B3%BC%EC%9E%A5</t>
+  </si>
+  <si>
+    <t>2조 4059억 2866만</t>
+  </si>
+  <si>
+    <t>사과닷</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EA%B3%BC%EB%8B%B7</t>
+  </si>
+  <si>
+    <t>2조 3266억 8637만</t>
+  </si>
+  <si>
+    <t>뽀뾰해봄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%BE%B0%ED%95%B4%EB%B4%84</t>
+  </si>
+  <si>
+    <t>1조 8072억 3038만</t>
+  </si>
+  <si>
+    <t>Eddy0825</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Eddy0825</t>
+  </si>
+  <si>
+    <t>1조 5159억 8227만</t>
+  </si>
+  <si>
+    <t>히히맘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%ED%9E%88%EB%A7%98</t>
+  </si>
+  <si>
+    <t>1조 3404억 2778만</t>
+  </si>
+  <si>
+    <t>토이감자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EC%9D%B4%EA%B0%90%EC%9E%90</t>
+  </si>
+  <si>
+    <t>1조 3297억 1328만</t>
+  </si>
+  <si>
+    <t>망치전문</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%98%EC%A0%84%EB%AC%B8</t>
+  </si>
+  <si>
+    <t>1조 2441억 8376만</t>
+  </si>
+  <si>
+    <t>돌격대원</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EA%B2%A9%EB%8C%80%EC%9B%90</t>
+  </si>
+  <si>
+    <t>1조 1548억 8804만</t>
+  </si>
+  <si>
+    <t>닉커</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%89%EC%BB%A4</t>
+  </si>
+  <si>
+    <t>1조 1455억 4997만</t>
+  </si>
+  <si>
+    <t>호츠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%B8%A0</t>
+  </si>
+  <si>
+    <t>1조 129억 3752만</t>
+  </si>
+  <si>
+    <t>핑와스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%91%EC%99%80%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>9422억 3151만</t>
+  </si>
+  <si>
+    <t>단풍a</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8Da</t>
+  </si>
+  <si>
+    <t>9328억 34만</t>
+  </si>
+  <si>
+    <t>문뚱식</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%9A%B1%EC%8B%9D</t>
+  </si>
+  <si>
+    <t>9221억 2396만</t>
+  </si>
+  <si>
+    <t>비숍덩구</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%88%8D%EB%8D%A9%EA%B5%AC</t>
+  </si>
+  <si>
+    <t>9200억 3546만</t>
+  </si>
+  <si>
+    <t>회원카드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9A%8C%EC%9B%90%EC%B9%B4%EB%93%9C</t>
+  </si>
+  <si>
+    <t>7913억 4751만</t>
+  </si>
+  <si>
+    <t>떼링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%96%BC%EB%A7%81</t>
+  </si>
+  <si>
+    <t>7499억 5629만</t>
+  </si>
+  <si>
+    <t>오보기다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%B3%B4%EA%B8%B0%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>6741억 7723만</t>
+  </si>
+  <si>
+    <t>로우머</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A1%9C%EC%9A%B0%EB%A8%B8</t>
+  </si>
+  <si>
+    <t>6583억 4222만</t>
+  </si>
+  <si>
+    <t>RIMS</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=RIMS</t>
+  </si>
+  <si>
+    <t>6512억 5748만</t>
+  </si>
+  <si>
+    <t>떵헤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%96%B5%ED%97%A4</t>
+  </si>
+  <si>
+    <t>6138억 6429만</t>
+  </si>
+  <si>
+    <t>오말랑</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%A7%90%EB%9E%91</t>
+  </si>
+  <si>
+    <t>5351억 4536만</t>
+  </si>
+  <si>
+    <t>직불카드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%81%EB%B6%88%EC%B9%B4%EB%93%9C</t>
+  </si>
+  <si>
+    <t>2442억 6948만</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>채채자매</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EC%B1%84%EC%9E%90%EB%A7%A4</t>
+  </si>
+  <si>
+    <t>1433억 9734만</t>
+  </si>
+  <si>
+    <t>MAKTO</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=MAKTO</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>113조 6505억 8775만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EB%AF%B8%ED%98%95</t>
+  </si>
+  <si>
+    <t>50조 6875억 1260만</t>
+  </si>
+  <si>
+    <t>민헤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%ED%97%A4</t>
+  </si>
+  <si>
+    <t>12조 8020억 1758만</t>
+  </si>
+  <si>
+    <t>세계챔피언</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EA%B3%84%EC%B1%94%ED%94%BC%EC%96%B8</t>
+  </si>
+  <si>
+    <t>10조 3718억 3648만</t>
+  </si>
+  <si>
+    <t>I라헬I</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=I%EB%9D%BC%ED%97%ACI</t>
+  </si>
+  <si>
+    <t>3조 3361억 4225만</t>
+  </si>
+  <si>
+    <t>건야웅</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B1%B4%EC%95%BC%EC%9B%85</t>
+  </si>
+  <si>
+    <t>2조 4543억 8797만</t>
+  </si>
+  <si>
+    <t>찐썽잉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B0%90%EC%8D%BD%EC%9E%89</t>
+  </si>
+  <si>
+    <t>2조 2859억 6115만</t>
+  </si>
+  <si>
+    <t>보꿍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EA%BF%8D</t>
+  </si>
+  <si>
+    <t>1조 7252억 2671만</t>
+  </si>
+  <si>
+    <t>소년가장원딜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EB%85%84%EA%B0%80%EC%9E%A5%EC%9B%90%EB%94%9C</t>
+  </si>
+  <si>
+    <t>1조 3553억 3451만</t>
+  </si>
+  <si>
+    <t>치킨v</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B9%98%ED%82%A8v</t>
+  </si>
+  <si>
+    <t>1조 2546억 5507만</t>
+  </si>
+  <si>
+    <t>레제내꺼야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A0%88%EC%A0%9C%EB%82%B4%EA%BA%BC%EC%95%BC</t>
+  </si>
+  <si>
+    <t>9440억 8488만</t>
+  </si>
+  <si>
+    <t>묨밍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%A8%EB%B0%8D</t>
+  </si>
+  <si>
+    <t>8657억 5632만</t>
+  </si>
+  <si>
+    <t>키죠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%EC%A3%A0</t>
+  </si>
+  <si>
+    <t>8583억 9432만</t>
+  </si>
+  <si>
+    <t>S2지존</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=S2%EC%A7%80%EC%A1%B4</t>
+  </si>
+  <si>
+    <t>8260억 7822만</t>
+  </si>
+  <si>
+    <t>하얀물개</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%96%80%EB%AC%BC%EA%B0%9C</t>
+  </si>
+  <si>
+    <t>7680억 3260만</t>
+  </si>
+  <si>
+    <t>초코냥부하</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%BD%94%EB%83%A5%EB%B6%80%ED%95%98</t>
+  </si>
+  <si>
+    <t>6544억 5291만</t>
+  </si>
+  <si>
+    <t>장빵구</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EB%B9%B5%EA%B5%AC</t>
+  </si>
+  <si>
+    <t>5600억 447만</t>
+  </si>
+  <si>
+    <t>레피스나2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A0%88%ED%94%BC%EC%8A%A4%EB%82%982</t>
+  </si>
+  <si>
+    <t>5053억 2083만</t>
+  </si>
+  <si>
+    <t>환불냠냠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EB%B6%88%EB%83%A0%EB%83%A0</t>
+  </si>
+  <si>
+    <t>5025억 7617만</t>
+  </si>
+  <si>
+    <t>혼자가최고</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%BC%EC%9E%90%EA%B0%80%EC%B5%9C%EA%B3%A0</t>
+  </si>
+  <si>
+    <t>4366억 6830만</t>
+  </si>
+  <si>
+    <t>깝용잉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%9D%EC%9A%A9%EC%9E%89</t>
+  </si>
+  <si>
+    <t>4268억 6235만</t>
+  </si>
+  <si>
+    <t>망복복</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EB%B3%B5%EB%B3%B5</t>
+  </si>
+  <si>
+    <t>3876억 9482만</t>
+  </si>
+  <si>
+    <t>모몬쌍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EB%AA%AC%EC%8C%8D</t>
+  </si>
+  <si>
+    <t>2497억 5284만</t>
+  </si>
+  <si>
+    <t>우주강아지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%A3%BC%EA%B0%95%EC%95%84%EC%A7%80</t>
+  </si>
+  <si>
+    <t>1874억 3020만</t>
+  </si>
+  <si>
+    <t>화가난꽝섭이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EA%B0%80%EB%82%9C%EA%BD%9D%EC%84%AD%EC%9D%B4</t>
+  </si>
+  <si>
     <t>92</t>
   </si>
   <si>
-    <t>2316억 2601만</t>
-  </si>
-  <si>
-    <t>긩섷</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%A9%EC%84%B7</t>
-  </si>
-  <si>
-    <t>93</t>
-  </si>
-  <si>
-    <t>1864억 9941만</t>
-  </si>
-  <si>
-    <t>샾갈배</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EA%B0%88%EB%B0%B0</t>
-  </si>
-  <si>
-    <t>1673억 5338만</t>
-  </si>
-  <si>
-    <t>최훈석개멋져</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%ED%9B%88%EC%84%9D%EA%B0%9C%EB%A9%8B%EC%A0%B8</t>
-  </si>
-  <si>
-    <t>90</t>
-  </si>
-  <si>
-    <t>1450억 7248만</t>
-  </si>
-  <si>
-    <t>샾사니서리당</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%82%AC%EB%8B%88%EC%84%9C%EB%A6%AC%EB%8B%B9</t>
-  </si>
-  <si>
-    <t>비숍</t>
-  </si>
-  <si>
-    <t>91</t>
-  </si>
-  <si>
-    <t>1296억 8675만</t>
-  </si>
-  <si>
-    <t>커피둥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%ED%94%BC%EB%91%A5</t>
-  </si>
-  <si>
-    <t>1192억 3496만</t>
-  </si>
-  <si>
-    <t>둥둥콩이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%91%A5%EB%91%A5%EC%BD%A9%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>19조 3773억 6624만</t>
-  </si>
-  <si>
-    <t>가온스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%98%A8%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>17조 3732억 4655만</t>
-  </si>
-  <si>
-    <t>증권보이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A6%9D%EA%B6%8C%EB%B3%B4%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>12조 6269억 9088만</t>
-  </si>
-  <si>
-    <t>Canary</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Canary</t>
-  </si>
-  <si>
-    <t>12조 3252억 5686만</t>
-  </si>
-  <si>
-    <t>처히</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%98%ED%9E%88</t>
-  </si>
-  <si>
-    <t>9조 8029억 8581만</t>
-  </si>
-  <si>
-    <t>환생의불꼬츠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EC%83%9D%EC%9D%98%EB%B6%88%EA%BC%AC%EC%B8%A0</t>
-  </si>
-  <si>
-    <t>9조 4367억 6924만</t>
-  </si>
-  <si>
-    <t>밍진</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%8D%EC%A7%84</t>
-  </si>
-  <si>
-    <t>8조 9166억 6911만</t>
-  </si>
-  <si>
-    <t>Naco</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Naco</t>
-  </si>
-  <si>
-    <t>6조 8631억 7813만</t>
-  </si>
-  <si>
-    <t>AKPS</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=AKPS</t>
-  </si>
-  <si>
-    <t>5조 7025억 8245만</t>
-  </si>
-  <si>
-    <t>로베르트슈만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A1%9C%EB%B2%A0%EB%A5%B4%ED%8A%B8%EC%8A%88%EB%A7%8C</t>
-  </si>
-  <si>
-    <t>4조 6954억 1280만</t>
-  </si>
-  <si>
-    <t>사나이기백황</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%82%98%EC%9D%B4%EA%B8%B0%EB%B0%B1%ED%99%A9</t>
-  </si>
-  <si>
-    <t>3조 6567억 2052만</t>
-  </si>
-  <si>
-    <t>평평이형</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%89%ED%8F%89%EC%9D%B4%ED%98%95</t>
-  </si>
-  <si>
-    <t>2조 9795억 1723만</t>
-  </si>
-  <si>
-    <t>토미오카상</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%AF%B8%EC%98%A4%EC%B9%B4%EC%83%81</t>
-  </si>
-  <si>
-    <t>2조 8348억 2352만</t>
-  </si>
-  <si>
-    <t>천칠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%B9%A0</t>
-  </si>
-  <si>
-    <t>2조 6702억 2482만</t>
-  </si>
-  <si>
-    <t>토니워터</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%8B%88%EC%9B%8C%ED%84%B0</t>
-  </si>
-  <si>
-    <t>2조 6162억 1545만</t>
-  </si>
-  <si>
-    <t>화살대</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%82%B4%EB%8C%80</t>
-  </si>
-  <si>
-    <t>2조 3627억 7524만</t>
-  </si>
-  <si>
-    <t>런닝래빗</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9F%B0%EB%8B%9D%EB%9E%98%EB%B9%97</t>
-  </si>
-  <si>
-    <t>2조 198억 5360만</t>
-  </si>
-  <si>
-    <t>펑풀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8E%91%ED%92%80</t>
-  </si>
-  <si>
-    <t>1조 9607억 4471만</t>
-  </si>
-  <si>
-    <t>피어난</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%BC%EC%96%B4%EB%82%9C</t>
-  </si>
-  <si>
-    <t>1조 6873억 4877만</t>
-  </si>
-  <si>
-    <t>샤스찌에</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%A4%EC%8A%A4%EC%B0%8C%EC%97%90</t>
-  </si>
-  <si>
-    <t>95</t>
-  </si>
-  <si>
-    <t>1조 2240억 35만</t>
-  </si>
-  <si>
-    <t>보동핑</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%8F%99%ED%95%91</t>
-  </si>
-  <si>
-    <t>1조 1390억 7233만</t>
-  </si>
-  <si>
-    <t>지니좋아요</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EB%8B%88%EC%A2%8B%EC%95%84%EC%9A%94</t>
-  </si>
-  <si>
-    <t>1조 666억 9786만</t>
-  </si>
-  <si>
-    <t>싸토루</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B8%ED%86%A0%EB%A3%A8</t>
-  </si>
-  <si>
-    <t>1조 477억 1901만</t>
-  </si>
-  <si>
-    <t>2026년1월30일</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=2026%EB%85%841%EC%9B%9430%EC%9D%BC</t>
-  </si>
-  <si>
-    <t>7942억 6933만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%8D%EC%B6%98%EC%82%BC</t>
-  </si>
-  <si>
-    <t>7940억 8278만</t>
-  </si>
-  <si>
-    <t>찐곽정근</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B0%90%EA%B3%BD%EC%A0%95%EA%B7%BC</t>
-  </si>
-  <si>
-    <t>7912억 9292만</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Targa</t>
-  </si>
-  <si>
-    <t>5665억 5826만</t>
-  </si>
-  <si>
-    <t>애둘이에요</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%A0%EB%91%98%EC%9D%B4%EC%97%90%EC%9A%94</t>
-  </si>
-  <si>
-    <t>5361억 4005만</t>
-  </si>
-  <si>
-    <t>짱창훈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%B1%EC%B0%BD%ED%9B%88</t>
-  </si>
-  <si>
-    <t>2736억 8603만</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>구리구리뽕리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%A6%AC%EA%B5%AC%EB%A6%AC%EB%BD%95%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>80</t>
-  </si>
-  <si>
-    <t>52억 8190만</t>
-  </si>
-  <si>
-    <t>마퀸</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%ED%80%B8</t>
-  </si>
-  <si>
-    <t>44조 51억 7989만</t>
-  </si>
-  <si>
-    <t>라면에계란탁</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EB%A9%B4%EC%97%90%EA%B3%84%EB%9E%80%ED%83%81</t>
-  </si>
-  <si>
-    <t>27조 5206억 3324만</t>
-  </si>
-  <si>
-    <t>에이비숍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EC%9D%B4%EB%B9%84%EC%88%8D</t>
-  </si>
-  <si>
-    <t>17조 4823억 394만</t>
-  </si>
-  <si>
-    <t>환불카드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EB%B6%88%EC%B9%B4%EB%93%9C</t>
-  </si>
-  <si>
-    <t>10조 6115억 767만</t>
-  </si>
-  <si>
-    <t>아빠카드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%B9%A0%EC%B9%B4%EB%93%9C</t>
-  </si>
-  <si>
-    <t>6조 2555억 5372만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%8F%84%EC%B9%B4%EB%93%9C</t>
-  </si>
-  <si>
-    <t>4조 7320억 482만</t>
-  </si>
-  <si>
-    <t>시글</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EA%B8%80</t>
-  </si>
-  <si>
-    <t>4조 156억 2084만</t>
-  </si>
-  <si>
-    <t>공사과장</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EC%82%AC%EA%B3%BC%EC%9E%A5</t>
-  </si>
-  <si>
-    <t>2조 4059억 2866만</t>
-  </si>
-  <si>
-    <t>사과닷</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EA%B3%BC%EB%8B%B7</t>
-  </si>
-  <si>
-    <t>2조 3266억 8637만</t>
-  </si>
-  <si>
-    <t>Eddy0825</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Eddy0825</t>
-  </si>
-  <si>
-    <t>1조 5159억 8227만</t>
-  </si>
-  <si>
-    <t>토이감자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EC%9D%B4%EA%B0%90%EC%9E%90</t>
-  </si>
-  <si>
-    <t>1조 3297억 1328만</t>
-  </si>
-  <si>
-    <t>망치전문</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%98%EC%A0%84%EB%AC%B8</t>
-  </si>
-  <si>
-    <t>1조 2310억 3373만</t>
-  </si>
-  <si>
-    <t>히히맘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%ED%9E%88%EB%A7%98</t>
-  </si>
-  <si>
-    <t>1조 2106억 9849만</t>
-  </si>
-  <si>
-    <t>돌격대원</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EA%B2%A9%EB%8C%80%EC%9B%90</t>
-  </si>
-  <si>
-    <t>1조 790억 9629만</t>
-  </si>
-  <si>
-    <t>닉커</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%89%EC%BB%A4</t>
-  </si>
-  <si>
-    <t>1조 468억 3525만</t>
-  </si>
-  <si>
-    <t>핑와스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%91%EC%99%80%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>9138억 670만</t>
-  </si>
-  <si>
-    <t>호츠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%B8%A0</t>
-  </si>
-  <si>
-    <t>9109억 2570만</t>
-  </si>
-  <si>
-    <t>문뚱식</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%9A%B1%EC%8B%9D</t>
-  </si>
-  <si>
-    <t>9052억 4694만</t>
-  </si>
-  <si>
-    <t>비숍덩구</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%88%8D%EB%8D%A9%EA%B5%AC</t>
-  </si>
-  <si>
-    <t>9009억 1957만</t>
-  </si>
-  <si>
-    <t>단풍a</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8Da</t>
-  </si>
-  <si>
-    <t>8257억 4459만</t>
-  </si>
-  <si>
-    <t>떼링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%96%BC%EB%A7%81</t>
-  </si>
-  <si>
-    <t>7458억 570만</t>
-  </si>
-  <si>
-    <t>회원카드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9A%8C%EC%9B%90%EC%B9%B4%EB%93%9C</t>
-  </si>
-  <si>
-    <t>7324억 3033만</t>
-  </si>
-  <si>
-    <t>오보기다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%B3%B4%EA%B8%B0%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>6741억 7723만</t>
-  </si>
-  <si>
-    <t>로우머</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A1%9C%EC%9A%B0%EB%A8%B8</t>
-  </si>
-  <si>
-    <t>6583억 4222만</t>
-  </si>
-  <si>
-    <t>떵헤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%96%B5%ED%97%A4</t>
-  </si>
-  <si>
-    <t>6048억 1731만</t>
-  </si>
-  <si>
-    <t>RIMS</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=RIMS</t>
-  </si>
-  <si>
-    <t>5957억 2487만</t>
-  </si>
-  <si>
-    <t>오말랑</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%A7%90%EB%9E%91</t>
-  </si>
-  <si>
-    <t>5071억 8373만</t>
-  </si>
-  <si>
-    <t>직불카드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%81%EB%B6%88%EC%B9%B4%EB%93%9C</t>
-  </si>
-  <si>
-    <t>2255억 948만</t>
-  </si>
-  <si>
-    <t>채채자매</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EC%B1%84%EC%9E%90%EB%A7%A4</t>
-  </si>
-  <si>
-    <t>1361억 398만</t>
-  </si>
-  <si>
-    <t>MAKTO</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=MAKTO</t>
-  </si>
-  <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>111조 2810억 2419만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EB%AF%B8%ED%98%95</t>
-  </si>
-  <si>
-    <t>50조 4896억 2038만</t>
-  </si>
-  <si>
-    <t>민헤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%ED%97%A4</t>
-  </si>
-  <si>
-    <t>11조 5168억 7356만</t>
-  </si>
-  <si>
-    <t>세계챔피언</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EA%B3%84%EC%B1%94%ED%94%BC%EC%96%B8</t>
-  </si>
-  <si>
-    <t>10조 3718억 3648만</t>
-  </si>
-  <si>
-    <t>I라헬I</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=I%EB%9D%BC%ED%97%ACI</t>
-  </si>
-  <si>
-    <t>3조 1958억 8672만</t>
-  </si>
-  <si>
-    <t>찐썽잉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B0%90%EC%8D%BD%EC%9E%89</t>
-  </si>
-  <si>
-    <t>2조 2203억 7898만</t>
-  </si>
-  <si>
-    <t>건야웅</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B1%B4%EC%95%BC%EC%9B%85</t>
-  </si>
-  <si>
-    <t>2조 393억 8672만</t>
-  </si>
-  <si>
-    <t>보꿍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EA%BF%8D</t>
-  </si>
-  <si>
-    <t>1조 7252억 2671만</t>
-  </si>
-  <si>
-    <t>소년가장원딜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EB%85%84%EA%B0%80%EC%9E%A5%EC%9B%90%EB%94%9C</t>
-  </si>
-  <si>
-    <t>1조 3553억 3451만</t>
-  </si>
-  <si>
-    <t>치킨v</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B9%98%ED%82%A8v</t>
-  </si>
-  <si>
-    <t>1조 2546억 5507만</t>
-  </si>
-  <si>
-    <t>레제내꺼야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A0%88%EC%A0%9C%EB%82%B4%EA%BA%BC%EC%95%BC</t>
-  </si>
-  <si>
-    <t>9440억 8488만</t>
-  </si>
-  <si>
-    <t>키죠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%EC%A3%A0</t>
-  </si>
-  <si>
-    <t>8460억 3852만</t>
-  </si>
-  <si>
-    <t>묨밍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%A8%EB%B0%8D</t>
-  </si>
-  <si>
-    <t>8330억 9581만</t>
-  </si>
-  <si>
-    <t>S2지존</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=S2%EC%A7%80%EC%A1%B4</t>
-  </si>
-  <si>
-    <t>8047억 7661만</t>
-  </si>
-  <si>
-    <t>하얀물개</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%96%80%EB%AC%BC%EA%B0%9C</t>
-  </si>
-  <si>
-    <t>7486억 9717만</t>
-  </si>
-  <si>
-    <t>초코냥부하</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%BD%94%EB%83%A5%EB%B6%80%ED%95%98</t>
-  </si>
-  <si>
-    <t>5783억 1003만</t>
-  </si>
-  <si>
-    <t>장빵구</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EB%B9%B5%EA%B5%AC</t>
-  </si>
-  <si>
-    <t>5600억 447만</t>
-  </si>
-  <si>
-    <t>환불냠냠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EB%B6%88%EB%83%A0%EB%83%A0</t>
-  </si>
-  <si>
-    <t>4690억 2113만</t>
-  </si>
-  <si>
-    <t>레피스나2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A0%88%ED%94%BC%EC%8A%A4%EB%82%982</t>
-  </si>
-  <si>
-    <t>4656억 7903만</t>
-  </si>
-  <si>
-    <t>혼자가최고</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%BC%EC%9E%90%EA%B0%80%EC%B5%9C%EA%B3%A0</t>
-  </si>
-  <si>
-    <t>4346억 9012만</t>
-  </si>
-  <si>
-    <t>깝용잉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%9D%EC%9A%A9%EC%9E%89</t>
-  </si>
-  <si>
-    <t>4268억 6235만</t>
-  </si>
-  <si>
-    <t>망복복</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EB%B3%B5%EB%B3%B5</t>
-  </si>
-  <si>
-    <t>3846억 1366만</t>
-  </si>
-  <si>
-    <t>모몬쌍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EB%AA%AC%EC%8C%8D</t>
-  </si>
-  <si>
-    <t>2461억 6727만</t>
-  </si>
-  <si>
-    <t>우주강아지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%A3%BC%EA%B0%95%EC%95%84%EC%A7%80</t>
-  </si>
-  <si>
-    <t>1874억 3020만</t>
-  </si>
-  <si>
-    <t>화가난꽝섭이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EA%B0%80%EB%82%9C%EA%BD%9D%EC%84%AD%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1719억 3297만</t>
+    <t>1787억 2037만</t>
+  </si>
+  <si>
+    <t>봉오리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%EC%98%A4%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>87</t>
+  </si>
+  <si>
+    <t>919억 4970만</t>
   </si>
   <si>
     <t>이진니</t>
@@ -1685,19 +1697,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%A7%84%EB%8B%88</t>
   </si>
   <si>
-    <t>847억 1891만</t>
-  </si>
-  <si>
-    <t>봉오리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%EC%98%A4%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>86</t>
-  </si>
-  <si>
-    <t>726억 6028만</t>
+    <t>902억 7225만</t>
   </si>
   <si>
     <t>만년설딸기</t>
@@ -1709,7 +1709,7 @@
     <t>84</t>
   </si>
   <si>
-    <t>225억 116만</t>
+    <t>230억 2754만</t>
   </si>
 </sst>
 </file>
@@ -2193,48 +2193,48 @@
         <v>29</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>20</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>20</v>
@@ -2249,7 +2249,7 @@
         <v>42</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2290,7 +2290,7 @@
         <v>52</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2331,7 +2331,7 @@
         <v>61</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -2545,10 +2545,10 @@
         <v>97</v>
       </c>
       <c r="H6" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>98</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>99</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -2559,16 +2559,16 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>102</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>79</v>
@@ -2580,7 +2580,7 @@
         <v>81</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -2591,16 +2591,16 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>106</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>79</v>
@@ -2609,7 +2609,7 @@
         <v>92</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>107</v>
@@ -2638,13 +2638,13 @@
         <v>79</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>73</v>
+        <v>111</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>87</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -2655,22 +2655,22 @@
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>115</v>
+        <v>73</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>87</v>
@@ -2766,7 +2766,7 @@
         <v>79</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>121</v>
@@ -2830,13 +2830,13 @@
         <v>79</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>115</v>
+        <v>73</v>
       </c>
       <c r="H15" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -2847,25 +2847,25 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>121</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>143</v>
@@ -2894,13 +2894,13 @@
         <v>79</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="H17" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>148</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -2911,28 +2911,28 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>153</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -2943,28 +2943,28 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="F19" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H19" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="I19" s="2" t="s">
         <v>156</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>157</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -2975,28 +2975,28 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>160</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>161</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -3007,16 +3007,16 @@
         <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="D21" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>163</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>164</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>79</v>
@@ -3025,10 +3025,10 @@
         <v>73</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3039,28 +3039,28 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>168</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>169</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3071,16 +3071,16 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="D23" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>172</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>79</v>
@@ -3092,7 +3092,7 @@
         <v>87</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3103,16 +3103,16 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="D24" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>175</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>176</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>79</v>
@@ -3121,10 +3121,10 @@
         <v>80</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3135,25 +3135,25 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="D25" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G25" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="F25" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="H25" s="2" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>181</v>
@@ -3182,13 +3182,13 @@
         <v>79</v>
       </c>
       <c r="G26" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>185</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>186</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -3199,28 +3199,28 @@
         <v>13</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="D27" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>190</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3231,16 +3231,16 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="D28" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>192</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>193</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>79</v>
@@ -3249,10 +3249,10 @@
         <v>80</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>121</v>
+        <v>87</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3263,16 +3263,16 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="D29" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>196</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>197</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>79</v>
@@ -3281,7 +3281,7 @@
         <v>73</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>147</v>
+        <v>197</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>198</v>
@@ -3426,16 +3426,16 @@
         <v>79</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>206</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3458,16 +3458,16 @@
         <v>79</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>209</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3490,16 +3490,16 @@
         <v>79</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>73</v>
+        <v>111</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>212</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -3522,16 +3522,16 @@
         <v>79</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>215</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3554,16 +3554,16 @@
         <v>79</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>218</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3571,7 +3571,7 @@
         <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>219</v>
@@ -3586,7 +3586,7 @@
         <v>79</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>115</v>
+        <v>73</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>87</v>
@@ -3595,7 +3595,7 @@
         <v>221</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -3603,7 +3603,7 @@
         <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>222</v>
@@ -3618,16 +3618,16 @@
         <v>79</v>
       </c>
       <c r="G8" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>225</v>
-      </c>
       <c r="J8" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -3638,28 +3638,28 @@
         <v>108</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>228</v>
-      </c>
       <c r="J9" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -3667,31 +3667,31 @@
         <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>231</v>
-      </c>
       <c r="J10" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -3702,28 +3702,28 @@
         <v>117</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>233</v>
-      </c>
       <c r="F11" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>121</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -3734,28 +3734,28 @@
         <v>123</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>237</v>
-      </c>
       <c r="J12" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -3766,28 +3766,28 @@
         <v>127</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>32</v>
+        <v>237</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>32</v>
+        <v>237</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>238</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>239</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -3810,16 +3810,16 @@
         <v>79</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>73</v>
+        <v>242</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>121</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -3830,28 +3830,28 @@
         <v>135</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -3859,31 +3859,31 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>87</v>
+        <v>155</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -3894,28 +3894,28 @@
         <v>144</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -3923,31 +3923,31 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>138</v>
+        <v>197</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -3955,31 +3955,31 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -3987,31 +3987,31 @@
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>73</v>
+        <v>111</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>147</v>
+        <v>197</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -4019,31 +4019,31 @@
         <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>147</v>
+        <v>197</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -4051,31 +4051,31 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -4083,31 +4083,31 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>266</v>
+        <v>197</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -4115,31 +4115,31 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>266</v>
+        <v>197</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -4147,31 +4147,31 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -4182,28 +4182,28 @@
         <v>182</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>278</v>
+        <v>33</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>278</v>
+        <v>33</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>279</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>73</v>
+        <v>120</v>
       </c>
       <c r="H26" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="I26" s="2" t="s">
-        <v>281</v>
-      </c>
       <c r="J26" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -4211,31 +4211,31 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="F27" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>284</v>
-      </c>
       <c r="J27" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -4243,31 +4243,31 @@
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H28" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="F28" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H28" s="2" t="s">
+      <c r="I28" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="I28" s="2" t="s">
-        <v>288</v>
-      </c>
       <c r="J28" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -4275,31 +4275,31 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="F29" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="F29" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>293</v>
-      </c>
       <c r="J29" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -4310,13 +4310,13 @@
         <v>199</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>79</v>
@@ -4325,13 +4325,13 @@
         <v>92</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -4373,6 +4373,1018 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J30"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="50.7109375" customWidth="1"/>
+    <col min="6" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="17.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J30"/>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1"/>
+    <hyperlink ref="E3" r:id="rId2"/>
+    <hyperlink ref="E4" r:id="rId3"/>
+    <hyperlink ref="E5" r:id="rId4"/>
+    <hyperlink ref="E6" r:id="rId5"/>
+    <hyperlink ref="E7" r:id="rId6"/>
+    <hyperlink ref="E8" r:id="rId7"/>
+    <hyperlink ref="E9" r:id="rId8"/>
+    <hyperlink ref="E10" r:id="rId9"/>
+    <hyperlink ref="E11" r:id="rId10"/>
+    <hyperlink ref="E12" r:id="rId11"/>
+    <hyperlink ref="E13" r:id="rId12"/>
+    <hyperlink ref="E14" r:id="rId13"/>
+    <hyperlink ref="E15" r:id="rId14"/>
+    <hyperlink ref="E16" r:id="rId15"/>
+    <hyperlink ref="E17" r:id="rId16"/>
+    <hyperlink ref="E18" r:id="rId17"/>
+    <hyperlink ref="E19" r:id="rId18"/>
+    <hyperlink ref="E20" r:id="rId19"/>
+    <hyperlink ref="E21" r:id="rId20"/>
+    <hyperlink ref="E22" r:id="rId21"/>
+    <hyperlink ref="E23" r:id="rId22"/>
+    <hyperlink ref="E24" r:id="rId23"/>
+    <hyperlink ref="E25" r:id="rId24"/>
+    <hyperlink ref="E26" r:id="rId25"/>
+    <hyperlink ref="E27" r:id="rId26"/>
+    <hyperlink ref="E28" r:id="rId27"/>
+    <hyperlink ref="E29" r:id="rId28"/>
+    <hyperlink ref="E30" r:id="rId29"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -4420,19 +5432,19 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>297</v>
+        <v>384</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>297</v>
+        <v>384</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>298</v>
+        <v>385</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>79</v>
@@ -4441,193 +5453,193 @@
         <v>86</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>299</v>
+        <v>386</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>300</v>
+        <v>387</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>300</v>
+        <v>387</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>301</v>
+        <v>388</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>115</v>
+        <v>73</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>302</v>
+        <v>389</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>303</v>
+        <v>390</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>303</v>
+        <v>390</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>304</v>
+        <v>391</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>73</v>
+        <v>378</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>305</v>
+        <v>392</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>89</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>306</v>
+        <v>393</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>306</v>
+        <v>393</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>307</v>
+        <v>394</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>73</v>
+        <v>242</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>308</v>
+        <v>395</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>94</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>309</v>
+        <v>396</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>309</v>
+        <v>396</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>310</v>
+        <v>397</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>87</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>311</v>
+        <v>398</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>312</v>
+        <v>399</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>312</v>
+        <v>399</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>313</v>
+        <v>400</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>73</v>
+        <v>378</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>87</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>314</v>
+        <v>401</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>315</v>
+        <v>52</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>315</v>
+        <v>52</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>316</v>
+        <v>402</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>73</v>
@@ -4636,746 +5648,746 @@
         <v>87</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>317</v>
+        <v>403</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>108</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>318</v>
+        <v>404</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>318</v>
+        <v>404</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>319</v>
+        <v>405</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>115</v>
+        <v>378</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>87</v>
+        <v>142</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>320</v>
+        <v>406</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>321</v>
+        <v>407</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>321</v>
+        <v>407</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>322</v>
+        <v>408</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>121</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>323</v>
+        <v>409</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>117</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>324</v>
+        <v>410</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>324</v>
+        <v>410</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>325</v>
+        <v>411</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>73</v>
+        <v>111</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>87</v>
+        <v>142</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>326</v>
+        <v>412</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>123</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>327</v>
+        <v>413</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>327</v>
+        <v>413</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>328</v>
+        <v>414</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>121</v>
+        <v>197</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>329</v>
+        <v>415</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>127</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>330</v>
+        <v>416</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>330</v>
+        <v>416</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>331</v>
+        <v>417</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>73</v>
+        <v>111</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>147</v>
+        <v>197</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>332</v>
+        <v>418</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>131</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>333</v>
+        <v>419</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>333</v>
+        <v>419</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>334</v>
+        <v>420</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>138</v>
+        <v>197</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>335</v>
+        <v>421</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>135</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>336</v>
+        <v>422</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>336</v>
+        <v>422</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>337</v>
+        <v>423</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>224</v>
+        <v>80</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>121</v>
+        <v>197</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>338</v>
+        <v>424</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>339</v>
+        <v>425</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>339</v>
+        <v>425</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>340</v>
+        <v>426</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>138</v>
+        <v>197</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>341</v>
+        <v>427</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>144</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>342</v>
+        <v>428</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>342</v>
+        <v>428</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>343</v>
+        <v>429</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>152</v>
+        <v>197</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>344</v>
+        <v>430</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>345</v>
+        <v>431</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>345</v>
+        <v>431</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>346</v>
+        <v>432</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>147</v>
+        <v>197</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>347</v>
+        <v>433</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>348</v>
+        <v>434</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>348</v>
+        <v>434</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>349</v>
+        <v>435</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>138</v>
+        <v>197</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>350</v>
+        <v>436</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>351</v>
+        <v>437</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>351</v>
+        <v>437</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>352</v>
+        <v>438</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>152</v>
+        <v>197</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>353</v>
+        <v>439</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>354</v>
+        <v>440</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>354</v>
+        <v>440</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>355</v>
+        <v>441</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>115</v>
+        <v>73</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>356</v>
+        <v>142</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>357</v>
+        <v>442</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>358</v>
+        <v>443</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>358</v>
+        <v>443</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>359</v>
+        <v>444</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>360</v>
+        <v>445</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>361</v>
+        <v>446</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>361</v>
+        <v>446</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>362</v>
+        <v>447</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>147</v>
+        <v>267</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>363</v>
+        <v>448</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>364</v>
+        <v>449</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>364</v>
+        <v>449</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>365</v>
+        <v>450</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>356</v>
+        <v>277</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>366</v>
+        <v>451</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>367</v>
+        <v>452</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>367</v>
+        <v>452</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>368</v>
+        <v>453</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>115</v>
+        <v>73</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>147</v>
+        <v>197</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>369</v>
+        <v>454</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>182</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>42</v>
+        <v>455</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>42</v>
+        <v>455</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>370</v>
+        <v>456</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>266</v>
+        <v>142</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>371</v>
+        <v>457</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>372</v>
+        <v>458</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>372</v>
+        <v>458</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>373</v>
+        <v>459</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>374</v>
+        <v>460</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>375</v>
+        <v>461</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>375</v>
+        <v>461</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>376</v>
+        <v>462</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>73</v>
+        <v>111</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>377</v>
+        <v>463</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>378</v>
+        <v>464</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>378</v>
+        <v>464</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>379</v>
+        <v>465</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>280</v>
+        <v>267</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>380</v>
+        <v>466</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>199</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>381</v>
+        <v>467</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>381</v>
+        <v>467</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>382</v>
+        <v>468</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>115</v>
+        <v>378</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>383</v>
+        <v>469</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>384</v>
+        <v>470</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>385</v>
+        <v>471</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>385</v>
+        <v>471</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>386</v>
+        <v>472</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>387</v>
+        <v>286</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>388</v>
+        <v>473</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -5416,1018 +6428,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J30"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" customWidth="1"/>
-    <col min="5" max="5" width="50.7109375" customWidth="1"/>
-    <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="17.7109375" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:J30"/>
-  <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1"/>
-    <hyperlink ref="E3" r:id="rId2"/>
-    <hyperlink ref="E4" r:id="rId3"/>
-    <hyperlink ref="E5" r:id="rId4"/>
-    <hyperlink ref="E6" r:id="rId5"/>
-    <hyperlink ref="E7" r:id="rId6"/>
-    <hyperlink ref="E8" r:id="rId7"/>
-    <hyperlink ref="E9" r:id="rId8"/>
-    <hyperlink ref="E10" r:id="rId9"/>
-    <hyperlink ref="E11" r:id="rId10"/>
-    <hyperlink ref="E12" r:id="rId11"/>
-    <hyperlink ref="E13" r:id="rId12"/>
-    <hyperlink ref="E14" r:id="rId13"/>
-    <hyperlink ref="E15" r:id="rId14"/>
-    <hyperlink ref="E16" r:id="rId15"/>
-    <hyperlink ref="E17" r:id="rId16"/>
-    <hyperlink ref="E18" r:id="rId17"/>
-    <hyperlink ref="E19" r:id="rId18"/>
-    <hyperlink ref="E20" r:id="rId19"/>
-    <hyperlink ref="E21" r:id="rId20"/>
-    <hyperlink ref="E22" r:id="rId21"/>
-    <hyperlink ref="E23" r:id="rId22"/>
-    <hyperlink ref="E24" r:id="rId23"/>
-    <hyperlink ref="E25" r:id="rId24"/>
-    <hyperlink ref="E26" r:id="rId25"/>
-    <hyperlink ref="E27" r:id="rId26"/>
-    <hyperlink ref="E28" r:id="rId27"/>
-    <hyperlink ref="E29" r:id="rId28"/>
-    <hyperlink ref="E30" r:id="rId29"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J29"/>
@@ -6483,13 +6483,13 @@
         <v>70</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>475</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>476</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>79</v>
@@ -6498,13 +6498,13 @@
         <v>73</v>
       </c>
       <c r="H2" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>478</v>
-      </c>
       <c r="J2" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -6521,7 +6521,7 @@
         <v>61</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>72</v>
@@ -6533,10 +6533,10 @@
         <v>74</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -6547,13 +6547,13 @@
         <v>83</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>481</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>482</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>79</v>
@@ -6562,13 +6562,13 @@
         <v>80</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -6579,13 +6579,13 @@
         <v>89</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>484</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>485</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>79</v>
@@ -6594,13 +6594,13 @@
         <v>73</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -6611,13 +6611,13 @@
         <v>94</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>487</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>488</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>79</v>
@@ -6629,10 +6629,10 @@
         <v>121</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -6640,31 +6640,31 @@
         <v>53</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>492</v>
-      </c>
       <c r="J7" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -6672,31 +6672,31 @@
         <v>53</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>494</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>495</v>
-      </c>
       <c r="J8" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -6707,13 +6707,13 @@
         <v>108</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>496</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>497</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>79</v>
@@ -6722,13 +6722,13 @@
         <v>73</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -6736,16 +6736,16 @@
         <v>53</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>499</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>500</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>79</v>
@@ -6754,13 +6754,13 @@
         <v>120</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -6771,13 +6771,13 @@
         <v>117</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>502</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>503</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>79</v>
@@ -6786,13 +6786,13 @@
         <v>73</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -6803,28 +6803,28 @@
         <v>123</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>507</v>
-      </c>
       <c r="J12" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -6835,13 +6835,13 @@
         <v>127</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>508</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>509</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>79</v>
@@ -6850,13 +6850,13 @@
         <v>73</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>147</v>
+        <v>197</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -6867,13 +6867,13 @@
         <v>131</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>511</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>512</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>79</v>
@@ -6882,13 +6882,13 @@
         <v>73</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>147</v>
+        <v>197</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -6899,13 +6899,13 @@
         <v>135</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>514</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>515</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>79</v>
@@ -6914,13 +6914,13 @@
         <v>86</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>356</v>
+        <v>267</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -6928,16 +6928,16 @@
         <v>53</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>517</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>518</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>79</v>
@@ -6946,13 +6946,13 @@
         <v>73</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>147</v>
+        <v>197</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -6963,13 +6963,13 @@
         <v>144</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>520</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>521</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>79</v>
@@ -6978,13 +6978,13 @@
         <v>80</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>356</v>
+        <v>267</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -6992,16 +6992,16 @@
         <v>53</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>523</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>524</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>79</v>
@@ -7010,13 +7010,13 @@
         <v>73</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -7024,31 +7024,31 @@
         <v>53</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>527</v>
       </c>
-      <c r="F19" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>528</v>
-      </c>
       <c r="J19" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -7056,31 +7056,31 @@
         <v>53</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="F20" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>531</v>
-      </c>
       <c r="J20" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -7088,31 +7088,31 @@
         <v>53</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="F21" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>534</v>
-      </c>
       <c r="J21" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -7120,16 +7120,16 @@
         <v>53</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>535</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>536</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>79</v>
@@ -7138,13 +7138,13 @@
         <v>73</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -7152,31 +7152,31 @@
         <v>53</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>539</v>
       </c>
-      <c r="F23" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>540</v>
-      </c>
       <c r="J23" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -7184,16 +7184,16 @@
         <v>53</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>541</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>542</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>79</v>
@@ -7202,13 +7202,13 @@
         <v>86</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -7216,16 +7216,16 @@
         <v>53</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>544</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>545</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>79</v>
@@ -7234,13 +7234,13 @@
         <v>73</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -7251,28 +7251,28 @@
         <v>182</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="F26" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H26" s="2" t="s">
         <v>548</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>276</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>549</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -7280,7 +7280,7 @@
         <v>53</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>550</v>
@@ -7295,16 +7295,16 @@
         <v>79</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>291</v>
+        <v>80</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>292</v>
+        <v>552</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -7312,31 +7312,31 @@
         <v>53</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>80</v>
+        <v>378</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>555</v>
+        <v>379</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>556</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -7344,7 +7344,7 @@
         <v>53</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>557</v>
@@ -7368,7 +7368,7 @@
         <v>560</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/reports/빅딜/빅딜_mgf_matched_5_guilds.xlsx
+++ b/reports/빅딜/빅딜_mgf_matched_5_guilds.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1578" uniqueCount="561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1578" uniqueCount="560">
   <si>
     <t>guild_name</t>
   </si>
@@ -683,7 +683,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%98%ED%9E%88</t>
   </si>
   <si>
-    <t>11조 4373억 7655만</t>
+    <t>13조 2156억 7422만</t>
   </si>
   <si>
     <t>환생의불꼬츠</t>
@@ -728,7 +728,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%82%98%EC%9D%B4%EA%B8%B0%EB%B0%B1%ED%99%A9</t>
   </si>
   <si>
-    <t>3조 7356억 3356만</t>
+    <t>3조 8303억 3845만</t>
   </si>
   <si>
     <t>토미오카상</t>
@@ -770,6 +770,15 @@
     <t>2조 6162억 1545만</t>
   </si>
   <si>
+    <t>펑풀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8E%91%ED%92%80</t>
+  </si>
+  <si>
+    <t>2조 4885억 7115만</t>
+  </si>
+  <si>
     <t>화살대</t>
   </si>
   <si>
@@ -779,22 +788,13 @@
     <t>2조 4258억 6186만</t>
   </si>
   <si>
-    <t>펑풀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8E%91%ED%92%80</t>
-  </si>
-  <si>
-    <t>2조 4059억 6852만</t>
-  </si>
-  <si>
     <t>런닝래빗</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%9F%B0%EB%8B%9D%EB%9E%98%EB%B9%97</t>
   </si>
   <si>
-    <t>2조 3545억 5014만</t>
+    <t>2조 4177억 8071만</t>
   </si>
   <si>
     <t>피어난</t>
@@ -821,7 +821,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%8F%99%ED%95%91</t>
   </si>
   <si>
-    <t>1조 1534억 4683만</t>
+    <t>1조 1820억 5434만</t>
   </si>
   <si>
     <t>싸토루</t>
@@ -860,24 +860,24 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B0%90%EA%B3%BD%EC%A0%95%EA%B7%BC</t>
   </si>
   <si>
+    <t>1조 24억 1640만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%8D%EC%B6%98%EC%82%BC</t>
+  </si>
+  <si>
+    <t>8747억 2403만</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Targa</t>
+  </si>
+  <si>
     <t>94</t>
   </si>
   <si>
-    <t>1조 24억 1640만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%8D%EC%B6%98%EC%82%BC</t>
-  </si>
-  <si>
-    <t>8747억 2403만</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Targa</t>
-  </si>
-  <si>
     <t>5665억 5826만</t>
   </si>
   <si>
@@ -911,7 +911,7 @@
     <t>80</t>
   </si>
   <si>
-    <t>52억 8190만</t>
+    <t>55억 5534만</t>
   </si>
   <si>
     <t>샾온</t>
@@ -1001,7 +1001,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EB%B0%A9%EB%8B%B4%EC%9A%94</t>
   </si>
   <si>
-    <t>3조 1952억 2814만</t>
+    <t>3조 4276억 8898만</t>
   </si>
   <si>
     <t>상산의조자룡</t>
@@ -1115,7 +1115,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%94%B1%EC%A7%80%EB%83%A5</t>
   </si>
   <si>
-    <t>4512억 5148만</t>
+    <t>4672억 6247만</t>
   </si>
   <si>
     <t>샾앤플랫</t>
@@ -1151,10 +1151,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%ED%9B%88%EC%84%9D%EA%B0%9C%EB%A9%8B%EC%A0%B8</t>
   </si>
   <si>
-    <t>90</t>
-  </si>
-  <si>
-    <t>1515억 6732만</t>
+    <t>91</t>
+  </si>
+  <si>
+    <t>1544억 6027만</t>
   </si>
   <si>
     <t>샾사니서리당</t>
@@ -1166,9 +1166,6 @@
     <t>비숍</t>
   </si>
   <si>
-    <t>91</t>
-  </si>
-  <si>
     <t>1346억 4398만</t>
   </si>
   <si>
@@ -1187,7 +1184,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%ED%80%B8</t>
   </si>
   <si>
-    <t>44조 6786억 4350만</t>
+    <t>45조 8042억 2273만</t>
   </si>
   <si>
     <t>라면에계란탁</t>
@@ -1196,7 +1193,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EB%A9%B4%EC%97%90%EA%B3%84%EB%9E%80%ED%83%81</t>
   </si>
   <si>
-    <t>29조 7729억 2533만</t>
+    <t>32조 9314억 2581만</t>
   </si>
   <si>
     <t>에이비숍</t>
@@ -1265,7 +1262,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%BE%B0%ED%95%B4%EB%B4%84</t>
   </si>
   <si>
-    <t>1조 8072억 3038만</t>
+    <t>2조 690억 7726만</t>
   </si>
   <si>
     <t>Eddy0825</t>
@@ -1283,7 +1280,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%ED%9E%88%EB%A7%98</t>
   </si>
   <si>
-    <t>1조 3404억 2778만</t>
+    <t>1조 3663억 941만</t>
   </si>
   <si>
     <t>토이감자</t>
@@ -1301,7 +1298,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%98%EC%A0%84%EB%AC%B8</t>
   </si>
   <si>
-    <t>1조 2441억 8376만</t>
+    <t>1조 3063억 1657만</t>
   </si>
   <si>
     <t>돌격대원</t>
@@ -1328,7 +1325,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%B8%A0</t>
   </si>
   <si>
-    <t>1조 129억 3752만</t>
+    <t>1조 389억 721만</t>
+  </si>
+  <si>
+    <t>회원카드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9A%8C%EC%9B%90%EC%B9%B4%EB%93%9C</t>
+  </si>
+  <si>
+    <t>9586억 327만</t>
   </si>
   <si>
     <t>핑와스</t>
@@ -1367,15 +1373,6 @@
     <t>9200억 3546만</t>
   </si>
   <si>
-    <t>회원카드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9A%8C%EC%9B%90%EC%B9%B4%EB%93%9C</t>
-  </si>
-  <si>
-    <t>7913억 4751만</t>
-  </si>
-  <si>
     <t>떼링</t>
   </si>
   <si>
@@ -1418,7 +1415,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%96%B5%ED%97%A4</t>
   </si>
   <si>
-    <t>6138억 6429만</t>
+    <t>6144억 6753만</t>
   </si>
   <si>
     <t>오말랑</t>
@@ -1427,7 +1424,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%A7%90%EB%9E%91</t>
   </si>
   <si>
-    <t>5351억 4536만</t>
+    <t>5601억 9209만</t>
   </si>
   <si>
     <t>직불카드</t>
@@ -1436,7 +1433,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%81%EB%B6%88%EC%B9%B4%EB%93%9C</t>
   </si>
   <si>
-    <t>2442억 6948만</t>
+    <t>2615억 5649만</t>
   </si>
   <si>
     <t>30</t>
@@ -3874,10 +3871,10 @@
         <v>79</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>249</v>
@@ -3906,10 +3903,10 @@
         <v>79</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>252</v>
@@ -4165,10 +4162,10 @@
         <v>86</v>
       </c>
       <c r="H25" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>277</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>278</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>34</v>
@@ -4188,7 +4185,7 @@
         <v>33</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>72</v>
@@ -4200,7 +4197,7 @@
         <v>267</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>34</v>
@@ -4214,13 +4211,13 @@
         <v>186</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>281</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>282</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>79</v>
@@ -4229,7 +4226,7 @@
         <v>73</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>283</v>
@@ -5081,7 +5078,7 @@
         <v>80</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>356</v>
@@ -5113,7 +5110,7 @@
         <v>86</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>359</v>
@@ -5145,7 +5142,7 @@
         <v>111</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>362</v>
@@ -5209,7 +5206,7 @@
         <v>73</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>368</v>
@@ -5305,10 +5302,10 @@
         <v>378</v>
       </c>
       <c r="H29" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>379</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>380</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>34</v>
@@ -5322,13 +5319,13 @@
         <v>199</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>381</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>382</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>79</v>
@@ -5337,10 +5334,10 @@
         <v>92</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>34</v>
@@ -5438,13 +5435,13 @@
         <v>70</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>384</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>385</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>79</v>
@@ -5456,7 +5453,7 @@
         <v>74</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>34</v>
@@ -5470,13 +5467,13 @@
         <v>76</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>387</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>388</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>79</v>
@@ -5488,7 +5485,7 @@
         <v>81</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>34</v>
@@ -5502,13 +5499,13 @@
         <v>83</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>390</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>391</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>79</v>
@@ -5520,7 +5517,7 @@
         <v>81</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>34</v>
@@ -5534,13 +5531,13 @@
         <v>89</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>393</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>394</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>79</v>
@@ -5552,7 +5549,7 @@
         <v>121</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>34</v>
@@ -5566,13 +5563,13 @@
         <v>94</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>396</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>397</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>79</v>
@@ -5584,7 +5581,7 @@
         <v>87</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>34</v>
@@ -5598,13 +5595,13 @@
         <v>99</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>399</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>400</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>79</v>
@@ -5616,7 +5613,7 @@
         <v>87</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>34</v>
@@ -5636,7 +5633,7 @@
         <v>52</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>72</v>
@@ -5648,7 +5645,7 @@
         <v>87</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>34</v>
@@ -5662,13 +5659,13 @@
         <v>108</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>404</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>405</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>79</v>
@@ -5680,7 +5677,7 @@
         <v>142</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>34</v>
@@ -5694,13 +5691,13 @@
         <v>113</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>407</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>408</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>79</v>
@@ -5712,7 +5709,7 @@
         <v>121</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>34</v>
@@ -5726,13 +5723,13 @@
         <v>117</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>410</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>411</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>79</v>
@@ -5744,7 +5741,7 @@
         <v>142</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>34</v>
@@ -5758,13 +5755,13 @@
         <v>123</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>413</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>414</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>79</v>
@@ -5776,7 +5773,7 @@
         <v>197</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>34</v>
@@ -5790,13 +5787,13 @@
         <v>127</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>416</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>417</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>79</v>
@@ -5808,7 +5805,7 @@
         <v>197</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>34</v>
@@ -5822,13 +5819,13 @@
         <v>131</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>419</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>420</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>79</v>
@@ -5840,7 +5837,7 @@
         <v>197</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>34</v>
@@ -5854,13 +5851,13 @@
         <v>135</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>422</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>423</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>79</v>
@@ -5872,7 +5869,7 @@
         <v>197</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>34</v>
@@ -5886,13 +5883,13 @@
         <v>139</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>425</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>426</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>79</v>
@@ -5904,7 +5901,7 @@
         <v>197</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>34</v>
@@ -5918,13 +5915,13 @@
         <v>144</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>428</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>429</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>79</v>
@@ -5936,7 +5933,7 @@
         <v>197</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>34</v>
@@ -5950,13 +5947,13 @@
         <v>148</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>431</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>432</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>79</v>
@@ -5968,7 +5965,7 @@
         <v>197</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>34</v>
@@ -5982,25 +5979,25 @@
         <v>152</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>435</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>436</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>34</v>
@@ -6014,25 +6011,25 @@
         <v>157</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>438</v>
-      </c>
       <c r="F20" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>111</v>
+        <v>73</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>197</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>34</v>
@@ -6046,25 +6043,25 @@
         <v>161</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>441</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>442</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>34</v>
@@ -6078,25 +6075,25 @@
         <v>165</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>444</v>
-      </c>
       <c r="F22" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>111</v>
+        <v>73</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>142</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>34</v>
@@ -6110,25 +6107,25 @@
         <v>169</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>447</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>448</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>34</v>
@@ -6142,13 +6139,13 @@
         <v>173</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>449</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>450</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>79</v>
@@ -6157,10 +6154,10 @@
         <v>111</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>34</v>
@@ -6174,13 +6171,13 @@
         <v>177</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>452</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>453</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>79</v>
@@ -6192,7 +6189,7 @@
         <v>197</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>34</v>
@@ -6206,13 +6203,13 @@
         <v>182</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>455</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>456</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>79</v>
@@ -6224,7 +6221,7 @@
         <v>142</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>34</v>
@@ -6238,13 +6235,13 @@
         <v>186</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>458</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>459</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>79</v>
@@ -6256,7 +6253,7 @@
         <v>267</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>34</v>
@@ -6270,13 +6267,13 @@
         <v>190</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>461</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>462</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>79</v>
@@ -6285,10 +6282,10 @@
         <v>111</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>34</v>
@@ -6302,13 +6299,13 @@
         <v>194</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>464</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>465</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>79</v>
@@ -6320,7 +6317,7 @@
         <v>267</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>34</v>
@@ -6334,13 +6331,13 @@
         <v>199</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>467</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>468</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>79</v>
@@ -6349,10 +6346,10 @@
         <v>378</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>34</v>
@@ -6363,16 +6360,16 @@
         <v>43</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="D31" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>471</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>472</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>79</v>
@@ -6384,7 +6381,7 @@
         <v>286</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>34</v>
@@ -6483,13 +6480,13 @@
         <v>70</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>474</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>475</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>79</v>
@@ -6498,10 +6495,10 @@
         <v>73</v>
       </c>
       <c r="H2" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>476</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>477</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>34</v>
@@ -6521,7 +6518,7 @@
         <v>61</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>72</v>
@@ -6533,7 +6530,7 @@
         <v>74</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>34</v>
@@ -6547,13 +6544,13 @@
         <v>83</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>480</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>481</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>79</v>
@@ -6565,7 +6562,7 @@
         <v>106</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>34</v>
@@ -6579,13 +6576,13 @@
         <v>89</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>483</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>484</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>79</v>
@@ -6597,7 +6594,7 @@
         <v>106</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>34</v>
@@ -6611,13 +6608,13 @@
         <v>94</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>486</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>487</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>79</v>
@@ -6629,7 +6626,7 @@
         <v>121</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>34</v>
@@ -6643,13 +6640,13 @@
         <v>99</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>489</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>490</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>79</v>
@@ -6661,7 +6658,7 @@
         <v>155</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>34</v>
@@ -6675,13 +6672,13 @@
         <v>103</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>492</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>493</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>79</v>
@@ -6693,7 +6690,7 @@
         <v>155</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>34</v>
@@ -6707,13 +6704,13 @@
         <v>108</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>495</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>496</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>79</v>
@@ -6725,7 +6722,7 @@
         <v>155</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>34</v>
@@ -6739,13 +6736,13 @@
         <v>113</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>498</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>499</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>79</v>
@@ -6757,7 +6754,7 @@
         <v>142</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>34</v>
@@ -6771,13 +6768,13 @@
         <v>117</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>501</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>502</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>79</v>
@@ -6789,7 +6786,7 @@
         <v>142</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>34</v>
@@ -6803,13 +6800,13 @@
         <v>123</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>504</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>505</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>79</v>
@@ -6821,7 +6818,7 @@
         <v>142</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>34</v>
@@ -6835,13 +6832,13 @@
         <v>127</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>507</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>508</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>79</v>
@@ -6853,7 +6850,7 @@
         <v>197</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>34</v>
@@ -6867,13 +6864,13 @@
         <v>131</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>510</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>511</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>79</v>
@@ -6885,7 +6882,7 @@
         <v>197</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>34</v>
@@ -6899,13 +6896,13 @@
         <v>135</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>513</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>514</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>79</v>
@@ -6917,7 +6914,7 @@
         <v>267</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>34</v>
@@ -6931,13 +6928,13 @@
         <v>139</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>516</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>517</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>79</v>
@@ -6949,7 +6946,7 @@
         <v>197</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>34</v>
@@ -6963,13 +6960,13 @@
         <v>144</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>519</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>520</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>79</v>
@@ -6981,7 +6978,7 @@
         <v>267</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>34</v>
@@ -6995,13 +6992,13 @@
         <v>148</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>522</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>523</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>79</v>
@@ -7010,10 +7007,10 @@
         <v>73</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>34</v>
@@ -7027,13 +7024,13 @@
         <v>152</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>525</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>526</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>79</v>
@@ -7045,7 +7042,7 @@
         <v>267</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>34</v>
@@ -7059,13 +7056,13 @@
         <v>157</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>528</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>529</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>79</v>
@@ -7074,10 +7071,10 @@
         <v>86</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>34</v>
@@ -7091,13 +7088,13 @@
         <v>161</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>531</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>532</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>79</v>
@@ -7109,7 +7106,7 @@
         <v>267</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>34</v>
@@ -7123,13 +7120,13 @@
         <v>165</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>534</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>535</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>79</v>
@@ -7138,10 +7135,10 @@
         <v>73</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>34</v>
@@ -7155,13 +7152,13 @@
         <v>169</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>537</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>538</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>79</v>
@@ -7170,10 +7167,10 @@
         <v>111</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>34</v>
@@ -7187,13 +7184,13 @@
         <v>173</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>540</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>541</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>79</v>
@@ -7202,10 +7199,10 @@
         <v>86</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>34</v>
@@ -7219,13 +7216,13 @@
         <v>177</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>543</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>544</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>79</v>
@@ -7237,7 +7234,7 @@
         <v>286</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>34</v>
@@ -7251,13 +7248,13 @@
         <v>182</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>546</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>547</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>79</v>
@@ -7266,10 +7263,10 @@
         <v>111</v>
       </c>
       <c r="H26" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>548</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>549</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>34</v>
@@ -7283,13 +7280,13 @@
         <v>186</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>550</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>551</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>79</v>
@@ -7298,10 +7295,10 @@
         <v>80</v>
       </c>
       <c r="H27" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>552</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>553</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>34</v>
@@ -7315,13 +7312,13 @@
         <v>190</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>554</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>555</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>79</v>
@@ -7330,10 +7327,10 @@
         <v>378</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>34</v>
@@ -7347,13 +7344,13 @@
         <v>194</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>557</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>558</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>79</v>
@@ -7362,10 +7359,10 @@
         <v>86</v>
       </c>
       <c r="H29" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>559</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>560</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>34</v>
